--- a/10_v1/financeiro/Jalecon_Modelo_Financeiro_v2.xlsx
+++ b/10_v1/financeiro/Jalecon_Modelo_Financeiro_v2.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1567,15 +1567,42 @@
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Como ler: H6 exige as três linhas com 'Sim' (margem, LTV/CAC e recuperação do CAC). H7 exige chegar a R$ 50 mi de receita anualizada em até 7 anos com no máximo 3% do mercado endereçável.</t>
-        </is>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>LTV/CAC ponderado pelo mix de novos clientes (mídia paga)</t>
+        </is>
+      </c>
+      <c r="B42" s="11">
+        <f>(Premissas!$F$47*Unidade!F6+Premissas!$F$52*Unidade!F7+Premissas!$F$57*Unidade!F8+Premissas!$F$63*Unidade!F9)/Premissas!$F$42</f>
+        <v/>
+      </c>
+      <c r="C42" s="11">
+        <f>(Premissas!$F$76*Unidade!F13+Premissas!$F$82*Unidade!F14+Premissas!$F$89*Unidade!F15)/Premissas!$F$70</f>
+        <v/>
+      </c>
+      <c r="D42" s="11">
+        <f>Premissas!$F$98</f>
+        <v/>
+      </c>
+      <c r="E42" s="3">
+        <f>IF(B42&gt;=Premissas!$F$98,"Sim","Não")</f>
+        <v/>
+      </c>
+      <c r="F42" s="3">
+        <f>IF(C42&gt;=Premissas!$F$98,"Sim","Não")</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Como ler: H6 exige as três linhas com 'Sim' (margem, LTV/CAC e recuperação do CAC). H7 exige chegar a R$ 50 mi de receita anualizada em até 7 anos com no máximo 3% do mercado endereçável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>As abas Cenarios e Sensibilidade são geradas pelo script sensibilidade_v2.py: são valores, não fórmulas. Ao mudar premissas, rode o script de novo.</t>
         </is>
@@ -1592,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -1652,6 +1679,13 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Versão 2.1 (20/10/2026): incorpora a contraprova. Impostos de lucro presumido desde o início; churn, CAC e capacidade dos especialistas do Modelo B pela regra pré-registrada; cobrança por consulta desligada (art. 59 do Código de Ética Médica); custos de implantação e de indicação; mídia proporcional à expansão; Agenda Cheia a partir do mês 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Limitações: churn e CAC ainda são referências de mercado, não medição própria; não há sazonalidade; as consultas atribuídas no Modelo B são suposição a validar em piloto.</t>
         </is>
@@ -1668,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1800,13 +1834,13 @@
         </is>
       </c>
       <c r="C9" s="28" t="n">
-        <v>0.11</v>
+        <v>0.163</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>0.11</v>
+        <v>0.163</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>0.11</v>
+        <v>0.163</v>
       </c>
       <c r="F9" s="27">
         <f>CHOOSE($C$3,C9,D9,E9)</f>
@@ -1814,7 +1848,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Simples Nacional com fator R (software e serviços); plano v0</t>
+          <t>v2.1: lucro presumido desde o início. O Simples não admite sócio pessoa jurídica, o que impede investidor institucional (contraprova)</t>
         </is>
       </c>
     </row>
@@ -3533,13 +3567,13 @@
         </is>
       </c>
       <c r="C70" s="29" t="n">
-        <v>7500</v>
+        <v>9000</v>
       </c>
       <c r="D70" s="29" t="n">
-        <v>5500</v>
+        <v>6500</v>
       </c>
       <c r="E70" s="29" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="F70" s="26">
         <f>CHOOSE($C$3,C70,D70,E70)</f>
@@ -3547,7 +3581,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Ticket maior pede venda assistida; recuperação do CAC em cerca de 8 meses no cenário base</t>
+          <t>v2.1: mesmo método do Modelo A (recuperação do CAC em cerca de 8 meses sobre a contribuição ponderada pelos planos)</t>
         </is>
       </c>
     </row>
@@ -3623,13 +3657,13 @@
         </is>
       </c>
       <c r="C73" s="29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D73" s="29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E73" s="29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F73" s="26">
         <f>CHOOSE($C$3,C73,D73,E73)</f>
@@ -3637,7 +3671,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Componente por resultado, inspirado na Zocdoc (US$ 35 a US$ 110 por paciente novo)</t>
+          <t>v2.1: desligado. Cobrar por paciente recebido pode ferir o art. 59 do Código de Ética Médica (contraprova); só volta com parecer jurídico favorável</t>
         </is>
       </c>
     </row>
@@ -3743,13 +3777,13 @@
         </is>
       </c>
       <c r="C77" s="28" t="n">
-        <v>0.045</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D77" s="28" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E77" s="28" t="n">
         <v>0.035</v>
-      </c>
-      <c r="E77" s="28" t="n">
-        <v>0.025</v>
       </c>
       <c r="F77" s="27">
         <f>CHOOSE($C$3,C77,D77,E77)</f>
@@ -3757,7 +3791,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Agências com contrato retêm de 1,6% a 2,4% ao mês; resultado medido e site hospedado ajudam a reter (relatório 03)</t>
+          <t>v2.1: regra pré-registrada (referência de software para pequenas empresas, 4% a 7%), porque o contrato é mensal. O valor de agência com contrato (2% a 3,5%) virou o cenário otimista</t>
         </is>
       </c>
     </row>
@@ -3803,13 +3837,13 @@
         </is>
       </c>
       <c r="C79" s="17" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D79" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E79" s="17" t="n">
         <v>70</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>90</v>
       </c>
       <c r="F79" s="8">
         <f>CHOOSE($C$3,C79,D79,E79)</f>
@@ -3817,7 +3851,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Especialista humano que supervisiona os agentes (agência tradicional: 10 a 15 contas por pessoa)</t>
+          <t>v2.1: agências trabalham com 5 a 30 contas por gerente (contraprova). O otimista (40 a 70) é a aposta a provar no piloto</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3941,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Suposição</t>
+          <t>Suposição (a partir do mês 9, como no PRD; antes vai para Presença)</t>
         </is>
       </c>
     </row>
@@ -3923,13 +3957,13 @@
         </is>
       </c>
       <c r="C83" s="28" t="n">
-        <v>0.04</v>
+        <v>0.065</v>
       </c>
       <c r="D83" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E83" s="28" t="n">
         <v>0.03</v>
-      </c>
-      <c r="E83" s="28" t="n">
-        <v>0.02</v>
       </c>
       <c r="F83" s="27">
         <f>CHOOSE($C$3,C83,D83,E83)</f>
@@ -3937,7 +3971,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Agências com contrato retêm de 1,6% a 2,4% ao mês; resultado medido e site hospedado ajudam a reter (relatório 03)</t>
+          <t>v2.1: regra pré-registrada (referência de software para pequenas empresas, 4% a 7%), porque o contrato é mensal. O valor de agência com contrato (2% a 3,5%) virou o cenário otimista</t>
         </is>
       </c>
     </row>
@@ -3983,13 +4017,13 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D85" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="D85" s="17" t="n">
+      <c r="E85" s="17" t="n">
         <v>40</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>50</v>
       </c>
       <c r="F85" s="8">
         <f>CHOOSE($C$3,C85,D85,E85)</f>
@@ -3997,7 +4031,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Especialista humano que supervisiona os agentes (agência tradicional: 10 a 15 contas por pessoa)</t>
+          <t>v2.1: agências trabalham com 5 a 30 contas por gerente (contraprova). O otimista (40 a 70) é a aposta a provar no piloto</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4151,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Suposição (a partir do mês 13; antes vai para Agenda Cheia)</t>
+          <t>Suposição (a partir do mês 13; antes vai para Agenda Cheia ou Presença)</t>
         </is>
       </c>
     </row>
@@ -4133,13 +4167,13 @@
         </is>
       </c>
       <c r="C90" s="28" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="D90" s="28" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E90" s="28" t="n">
         <v>0.022</v>
-      </c>
-      <c r="E90" s="28" t="n">
-        <v>0.015</v>
       </c>
       <c r="F90" s="27">
         <f>CHOOSE($C$3,C90,D90,E90)</f>
@@ -4147,7 +4181,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>Agências com contrato retêm de 1,6% a 2,4% ao mês; resultado medido e site hospedado ajudam a reter (relatório 03)</t>
+          <t>v2.1: regra pré-registrada (referência de software para pequenas empresas, 4% a 7%), porque o contrato é mensal. O valor de agência com contrato (2% a 3,5%) virou o cenário otimista</t>
         </is>
       </c>
     </row>
@@ -4193,13 +4227,13 @@
         </is>
       </c>
       <c r="C92" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="D92" s="17" t="n">
+      <c r="E92" s="17" t="n">
         <v>15</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>20</v>
       </c>
       <c r="F92" s="8">
         <f>CHOOSE($C$3,C92,D92,E92)</f>
@@ -4207,7 +4241,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Especialista humano que supervisiona os agentes (agência tradicional: 10 a 15 contas por pessoa)</t>
+          <t>v2.1: agências trabalham com 5 a 30 contas por gerente (contraprova). O otimista (40 a 70) é a aposta a provar no piloto</t>
         </is>
       </c>
     </row>
@@ -4438,6 +4472,176 @@
       <c r="G101" s="3" t="inlineStr">
         <is>
           <t>Plano v1, seção 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>7. Ajustes da contraprova (v2.1, 20/10/2026)</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Premissa</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>Otimista</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>Usado</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>Fonte ou justificativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Modelo A: custo de implantação por cliente novo</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="C105" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="D105" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="E105" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="F105" s="26">
+        <f>CHOOSE($C$3,C105,D105,E105)</f>
+        <v/>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Onboarding assistido; antes a taxa de implantação era receita sem custo (contraprova)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Modelo B: custo de implantação por cliente novo</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="C106" s="29" t="n">
+        <v>900</v>
+      </c>
+      <c r="D106" s="29" t="n">
+        <v>600</v>
+      </c>
+      <c r="E106" s="29" t="n">
+        <v>400</v>
+      </c>
+      <c r="F106" s="26">
+        <f>CHOOSE($C$3,C106,D106,E106)</f>
+        <v/>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Cerca de 6 horas de especialista mais ferramentas para marca, site e perfil no Google</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Modelo A: custo por cliente indicado (mês grátis)</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="C107" s="29" t="n">
+        <v>697</v>
+      </c>
+      <c r="D107" s="29" t="n">
+        <v>697</v>
+      </c>
+      <c r="E107" s="29" t="n">
+        <v>697</v>
+      </c>
+      <c r="F107" s="26">
+        <f>CHOOSE($C$3,C107,D107,E107)</f>
+        <v/>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Programa de indicação: um mês grátis; antes sem custo (contraprova)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Modelo B: custo por cliente indicado (mês grátis)</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="C108" s="29" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D108" s="29" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E108" s="29" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F108" s="26">
+        <f>CHOOSE($C$3,C108,D108,E108)</f>
+        <v/>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Um mês grátis na mensalidade média ponderada</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4680,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Contribuição = mensalidade e consultas, menos impostos (alíquota inicial), meios de pagamento, custo direto e parte do especialista humano.</t>
+          <t>Contribuição = mensalidade e consultas, menos impostos (alíquota cheia), meios de pagamento, custo direto e parte do especialista humano. LTV = contribuição / churn + taxa de implantação - custo de implantação.</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4757,7 @@
         <v/>
       </c>
       <c r="C6" s="26">
-        <f>B6*(1-Premissas!$F$9-Premissas!$F$11)-Premissas!$F$49</f>
+        <f>B6*(1-Premissas!$F$10-Premissas!$F$11)-Premissas!$F$49</f>
         <v/>
       </c>
       <c r="D6" s="27">
@@ -4565,7 +4769,7 @@
         <v/>
       </c>
       <c r="F6" s="26">
-        <f>C6/E6</f>
+        <f>C6/E6+Premissas!$F$46-Premissas!$F$105</f>
         <v/>
       </c>
       <c r="G6" s="26">
@@ -4592,7 +4796,7 @@
         <v/>
       </c>
       <c r="C7" s="26">
-        <f>B7*(1-Premissas!$F$9-Premissas!$F$11)-Premissas!$F$54</f>
+        <f>B7*(1-Premissas!$F$10-Premissas!$F$11)-Premissas!$F$54</f>
         <v/>
       </c>
       <c r="D7" s="27">
@@ -4604,7 +4808,7 @@
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>C7/E7</f>
+        <f>C7/E7+Premissas!$F$51-Premissas!$F$105</f>
         <v/>
       </c>
       <c r="G7" s="26">
@@ -4631,7 +4835,7 @@
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>B8*(1-Premissas!$F$9-Premissas!$F$11)-Premissas!$F$59-Premissas!$F$44/Premissas!$F$60</f>
+        <f>B8*(1-Premissas!$F$10-Premissas!$F$11)-Premissas!$F$59-Premissas!$F$44/Premissas!$F$60</f>
         <v/>
       </c>
       <c r="D8" s="27">
@@ -4643,7 +4847,7 @@
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>C8/E8</f>
+        <f>C8/E8+Premissas!$F$56-Premissas!$F$105</f>
         <v/>
       </c>
       <c r="G8" s="26">
@@ -4670,7 +4874,7 @@
         <v/>
       </c>
       <c r="C9" s="26">
-        <f>B9*(1-Premissas!$F$9-Premissas!$F$11)-Premissas!$F$65-Premissas!$F$44/Premissas!$F$66</f>
+        <f>B9*(1-Premissas!$F$10-Premissas!$F$11)-Premissas!$F$65-Premissas!$F$44/Premissas!$F$66</f>
         <v/>
       </c>
       <c r="D9" s="27">
@@ -4682,7 +4886,7 @@
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>C9/E9</f>
+        <f>C9/E9+Premissas!$F$62-Premissas!$F$105</f>
         <v/>
       </c>
       <c r="G9" s="26">
@@ -4771,7 +4975,7 @@
         <v/>
       </c>
       <c r="C13" s="26">
-        <f>B13*(1-Premissas!$F$9-Premissas!$F$11)-Premissas!$F$78-Premissas!$F$72/Premissas!$F$79</f>
+        <f>B13*(1-Premissas!$F$10-Premissas!$F$11)-Premissas!$F$78-Premissas!$F$72/Premissas!$F$79</f>
         <v/>
       </c>
       <c r="D13" s="27">
@@ -4783,7 +4987,7 @@
         <v/>
       </c>
       <c r="F13" s="26">
-        <f>C13/E13</f>
+        <f>C13/E13+Premissas!$F$75-Premissas!$F$106</f>
         <v/>
       </c>
       <c r="G13" s="26">
@@ -4810,7 +5014,7 @@
         <v/>
       </c>
       <c r="C14" s="26">
-        <f>B14*(1-Premissas!$F$9-Premissas!$F$11)-Premissas!$F$84-Premissas!$F$72/Premissas!$F$85</f>
+        <f>B14*(1-Premissas!$F$10-Premissas!$F$11)-Premissas!$F$84-Premissas!$F$72/Premissas!$F$85</f>
         <v/>
       </c>
       <c r="D14" s="27">
@@ -4822,7 +5026,7 @@
         <v/>
       </c>
       <c r="F14" s="26">
-        <f>C14/E14</f>
+        <f>C14/E14+Premissas!$F$81-Premissas!$F$106</f>
         <v/>
       </c>
       <c r="G14" s="26">
@@ -4849,7 +5053,7 @@
         <v/>
       </c>
       <c r="C15" s="26">
-        <f>B15*(1-Premissas!$F$9-Premissas!$F$11)-Premissas!$F$91-Premissas!$F$72/Premissas!$F$92</f>
+        <f>B15*(1-Premissas!$F$10-Premissas!$F$11)-Premissas!$F$91-Premissas!$F$72/Premissas!$F$92</f>
         <v/>
       </c>
       <c r="D15" s="27">
@@ -4861,7 +5065,7 @@
         <v/>
       </c>
       <c r="F15" s="26">
-        <f>C15/E15</f>
+        <f>C15/E15+Premissas!$F$88-Premissas!$F$106</f>
         <v/>
       </c>
       <c r="G15" s="26">
@@ -6289,339 +6493,339 @@
         </is>
       </c>
       <c r="C8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,C3)*C4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,C3)*C4*C5</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,D3)*D4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,D3)*D4*D5</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,E3)*E4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,E3)*E4*E5</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,F3)*F4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,F3)*F4*F5</f>
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,G3)*G4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,G3)*G4*G5</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,H3)*H4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,H3)*H4*H5</f>
         <v/>
       </c>
       <c r="I8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,I3)*I4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,I3)*I4*I5</f>
         <v/>
       </c>
       <c r="J8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,J3)*J4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,J3)*J4*J5</f>
         <v/>
       </c>
       <c r="K8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,K3)*K4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,K3)*K4*K5</f>
         <v/>
       </c>
       <c r="L8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,L3)*L4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,L3)*L4*L5</f>
         <v/>
       </c>
       <c r="M8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,M3)*M4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,M3)*M4*M5</f>
         <v/>
       </c>
       <c r="N8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,N3)*N4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,N3)*N4*N5</f>
         <v/>
       </c>
       <c r="O8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,O3)*O4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,O3)*O4*O5</f>
         <v/>
       </c>
       <c r="P8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,P3)*P4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,P3)*P4*P5</f>
         <v/>
       </c>
       <c r="Q8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,Q3)*Q4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,Q3)*Q4*Q5</f>
         <v/>
       </c>
       <c r="R8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,R3)*R4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,R3)*R4*R5</f>
         <v/>
       </c>
       <c r="S8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,S3)*S4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,S3)*S4*S5</f>
         <v/>
       </c>
       <c r="T8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,T3)*T4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,T3)*T4*T5</f>
         <v/>
       </c>
       <c r="U8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,U3)*U4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,U3)*U4*U5</f>
         <v/>
       </c>
       <c r="V8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,V3)*V4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,V3)*V4*V5</f>
         <v/>
       </c>
       <c r="W8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,W3)*W4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,W3)*W4*W5</f>
         <v/>
       </c>
       <c r="X8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,X3)*X4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,X3)*X4*X5</f>
         <v/>
       </c>
       <c r="Y8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,Y3)*Y4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,Y3)*Y4*Y5</f>
         <v/>
       </c>
       <c r="Z8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,Z3)*Z4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,Z3)*Z4*Z5</f>
         <v/>
       </c>
       <c r="AA8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AA3)*AA4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AA3)*AA4*AA5</f>
         <v/>
       </c>
       <c r="AB8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AB3)*AB4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AB3)*AB4*AB5</f>
         <v/>
       </c>
       <c r="AC8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AC3)*AC4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AC3)*AC4*AC5</f>
         <v/>
       </c>
       <c r="AD8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AD3)*AD4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AD3)*AD4*AD5</f>
         <v/>
       </c>
       <c r="AE8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AE3)*AE4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AE3)*AE4*AE5</f>
         <v/>
       </c>
       <c r="AF8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AF3)*AF4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AF3)*AF4*AF5</f>
         <v/>
       </c>
       <c r="AG8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AG3)*AG4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AG3)*AG4*AG5</f>
         <v/>
       </c>
       <c r="AH8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AH3)*AH4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AH3)*AH4*AH5</f>
         <v/>
       </c>
       <c r="AI8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AI3)*AI4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AI3)*AI4*AI5</f>
         <v/>
       </c>
       <c r="AJ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AJ3)*AJ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AJ3)*AJ4*AJ5</f>
         <v/>
       </c>
       <c r="AK8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AK3)*AK4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AK3)*AK4*AK5</f>
         <v/>
       </c>
       <c r="AL8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AL3)*AL4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AL3)*AL4*AL5</f>
         <v/>
       </c>
       <c r="AM8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AM3)*AM4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AM3)*AM4*AM5</f>
         <v/>
       </c>
       <c r="AN8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AN3)*AN4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AN3)*AN4*AN5</f>
         <v/>
       </c>
       <c r="AO8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AO3)*AO4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AO3)*AO4*AO5</f>
         <v/>
       </c>
       <c r="AP8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AP3)*AP4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AP3)*AP4*AP5</f>
         <v/>
       </c>
       <c r="AQ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AQ3)*AQ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AQ3)*AQ4*AQ5</f>
         <v/>
       </c>
       <c r="AR8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AR3)*AR4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AR3)*AR4*AR5</f>
         <v/>
       </c>
       <c r="AS8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AS3)*AS4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AS3)*AS4*AS5</f>
         <v/>
       </c>
       <c r="AT8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AT3)*AT4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AT3)*AT4*AT5</f>
         <v/>
       </c>
       <c r="AU8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AU3)*AU4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AU3)*AU4*AU5</f>
         <v/>
       </c>
       <c r="AV8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AV3)*AV4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AV3)*AV4*AV5</f>
         <v/>
       </c>
       <c r="AW8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AW3)*AW4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AW3)*AW4*AW5</f>
         <v/>
       </c>
       <c r="AX8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AX3)*AX4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AX3)*AX4*AX5</f>
         <v/>
       </c>
       <c r="AY8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AY3)*AY4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AY3)*AY4*AY5</f>
         <v/>
       </c>
       <c r="AZ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AZ3)*AZ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AZ3)*AZ4*AZ5</f>
         <v/>
       </c>
       <c r="BA8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BA3)*BA4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BA3)*BA4*BA5</f>
         <v/>
       </c>
       <c r="BB8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BB3)*BB4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BB3)*BB4*BB5</f>
         <v/>
       </c>
       <c r="BC8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BC3)*BC4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BC3)*BC4*BC5</f>
         <v/>
       </c>
       <c r="BD8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BD3)*BD4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BD3)*BD4*BD5</f>
         <v/>
       </c>
       <c r="BE8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BE3)*BE4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BE3)*BE4*BE5</f>
         <v/>
       </c>
       <c r="BF8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BF3)*BF4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BF3)*BF4*BF5</f>
         <v/>
       </c>
       <c r="BG8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BG3)*BG4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BG3)*BG4*BG5</f>
         <v/>
       </c>
       <c r="BH8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BH3)*BH4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BH3)*BH4*BH5</f>
         <v/>
       </c>
       <c r="BI8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BI3)*BI4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BI3)*BI4*BI5</f>
         <v/>
       </c>
       <c r="BJ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BJ3)*BJ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BJ3)*BJ4*BJ5</f>
         <v/>
       </c>
       <c r="BK8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BK3)*BK4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BK3)*BK4*BK5</f>
         <v/>
       </c>
       <c r="BL8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BL3)*BL4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BL3)*BL4*BL5</f>
         <v/>
       </c>
       <c r="BM8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BM3)*BM4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BM3)*BM4*BM5</f>
         <v/>
       </c>
       <c r="BN8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BN3)*BN4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BN3)*BN4*BN5</f>
         <v/>
       </c>
       <c r="BO8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BO3)*BO4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BO3)*BO4*BO5</f>
         <v/>
       </c>
       <c r="BP8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BP3)*BP4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BP3)*BP4*BP5</f>
         <v/>
       </c>
       <c r="BQ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BQ3)*BQ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BQ3)*BQ4*BQ5</f>
         <v/>
       </c>
       <c r="BR8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BR3)*BR4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BR3)*BR4*BR5</f>
         <v/>
       </c>
       <c r="BS8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BS3)*BS4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BS3)*BS4*BS5</f>
         <v/>
       </c>
       <c r="BT8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BT3)*BT4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BT3)*BT4*BT5</f>
         <v/>
       </c>
       <c r="BU8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BU3)*BU4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BU3)*BU4*BU5</f>
         <v/>
       </c>
       <c r="BV8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BV3)*BV4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BV3)*BV4*BV5</f>
         <v/>
       </c>
       <c r="BW8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BW3)*BW4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BW3)*BW4*BW5</f>
         <v/>
       </c>
       <c r="BX8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BX3)*BX4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BX3)*BX4*BX5</f>
         <v/>
       </c>
       <c r="BY8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BY3)*BY4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BY3)*BY4*BY5</f>
         <v/>
       </c>
       <c r="BZ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BZ3)*BZ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BZ3)*BZ4*BZ5</f>
         <v/>
       </c>
       <c r="CA8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CA3)*CA4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CA3)*CA4*CA5</f>
         <v/>
       </c>
       <c r="CB8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CB3)*CB4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CB3)*CB4*CB5</f>
         <v/>
       </c>
       <c r="CC8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CC3)*CC4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CC3)*CC4*CC5</f>
         <v/>
       </c>
       <c r="CD8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CD3)*CD4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CD3)*CD4*CD5</f>
         <v/>
       </c>
       <c r="CE8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CE3)*CE4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CE3)*CE4*CE5</f>
         <v/>
       </c>
       <c r="CF8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CF3)*CF4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CF3)*CF4*CF5</f>
         <v/>
       </c>
       <c r="CG8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CG3)*CG4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CG3)*CG4*CG5</f>
         <v/>
       </c>
       <c r="CH8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CH3)*CH4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CH3)*CH4*CH5</f>
         <v/>
       </c>
     </row>
@@ -6632,339 +6836,339 @@
         </is>
       </c>
       <c r="C9" s="12">
-        <f>C8/Premissas!$F$42*C5</f>
+        <f>C8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="D9" s="12">
-        <f>D8/Premissas!$F$42*D5</f>
+        <f>D8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>E8/Premissas!$F$42*E5</f>
+        <f>E8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>F8/Premissas!$F$42*F5</f>
+        <f>F8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>G8/Premissas!$F$42*G5</f>
+        <f>G8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>H8/Premissas!$F$42*H5</f>
+        <f>H8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="I9" s="12">
-        <f>I8/Premissas!$F$42*I5</f>
+        <f>I8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="J9" s="12">
-        <f>J8/Premissas!$F$42*J5</f>
+        <f>J8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="K9" s="12">
-        <f>K8/Premissas!$F$42*K5</f>
+        <f>K8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="L9" s="12">
-        <f>L8/Premissas!$F$42*L5</f>
+        <f>L8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="M9" s="12">
-        <f>M8/Premissas!$F$42*M5</f>
+        <f>M8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="N9" s="12">
-        <f>N8/Premissas!$F$42*N5</f>
+        <f>N8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="O9" s="12">
-        <f>O8/Premissas!$F$42*O5</f>
+        <f>O8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="P9" s="12">
-        <f>P8/Premissas!$F$42*P5</f>
+        <f>P8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="Q9" s="12">
-        <f>Q8/Premissas!$F$42*Q5</f>
+        <f>Q8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="R9" s="12">
-        <f>R8/Premissas!$F$42*R5</f>
+        <f>R8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="S9" s="12">
-        <f>S8/Premissas!$F$42*S5</f>
+        <f>S8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="T9" s="12">
-        <f>T8/Premissas!$F$42*T5</f>
+        <f>T8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="U9" s="12">
-        <f>U8/Premissas!$F$42*U5</f>
+        <f>U8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="V9" s="12">
-        <f>V8/Premissas!$F$42*V5</f>
+        <f>V8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="W9" s="12">
-        <f>W8/Premissas!$F$42*W5</f>
+        <f>W8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="X9" s="12">
-        <f>X8/Premissas!$F$42*X5</f>
+        <f>X8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="Y9" s="12">
-        <f>Y8/Premissas!$F$42*Y5</f>
+        <f>Y8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="Z9" s="12">
-        <f>Z8/Premissas!$F$42*Z5</f>
+        <f>Z8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>AA8/Premissas!$F$42*AA5</f>
+        <f>AA8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AB9" s="12">
-        <f>AB8/Premissas!$F$42*AB5</f>
+        <f>AB8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AC9" s="12">
-        <f>AC8/Premissas!$F$42*AC5</f>
+        <f>AC8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AD9" s="12">
-        <f>AD8/Premissas!$F$42*AD5</f>
+        <f>AD8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AE9" s="12">
-        <f>AE8/Premissas!$F$42*AE5</f>
+        <f>AE8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AF9" s="12">
-        <f>AF8/Premissas!$F$42*AF5</f>
+        <f>AF8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>AG8/Premissas!$F$42*AG5</f>
+        <f>AG8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AH9" s="12">
-        <f>AH8/Premissas!$F$42*AH5</f>
+        <f>AH8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AI9" s="12">
-        <f>AI8/Premissas!$F$42*AI5</f>
+        <f>AI8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AJ9" s="12">
-        <f>AJ8/Premissas!$F$42*AJ5</f>
+        <f>AJ8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AK9" s="12">
-        <f>AK8/Premissas!$F$42*AK5</f>
+        <f>AK8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AL9" s="12">
-        <f>AL8/Premissas!$F$42*AL5</f>
+        <f>AL8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AM9" s="12">
-        <f>AM8/Premissas!$F$42*AM5</f>
+        <f>AM8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AN9" s="12">
-        <f>AN8/Premissas!$F$42*AN5</f>
+        <f>AN8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AO9" s="12">
-        <f>AO8/Premissas!$F$42*AO5</f>
+        <f>AO8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AP9" s="12">
-        <f>AP8/Premissas!$F$42*AP5</f>
+        <f>AP8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AQ9" s="12">
-        <f>AQ8/Premissas!$F$42*AQ5</f>
+        <f>AQ8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AR9" s="12">
-        <f>AR8/Premissas!$F$42*AR5</f>
+        <f>AR8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AS9" s="12">
-        <f>AS8/Premissas!$F$42*AS5</f>
+        <f>AS8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AT9" s="12">
-        <f>AT8/Premissas!$F$42*AT5</f>
+        <f>AT8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AU9" s="12">
-        <f>AU8/Premissas!$F$42*AU5</f>
+        <f>AU8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AV9" s="12">
-        <f>AV8/Premissas!$F$42*AV5</f>
+        <f>AV8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AW9" s="12">
-        <f>AW8/Premissas!$F$42*AW5</f>
+        <f>AW8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AX9" s="12">
-        <f>AX8/Premissas!$F$42*AX5</f>
+        <f>AX8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AY9" s="12">
-        <f>AY8/Premissas!$F$42*AY5</f>
+        <f>AY8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="AZ9" s="12">
-        <f>AZ8/Premissas!$F$42*AZ5</f>
+        <f>AZ8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BA9" s="12">
-        <f>BA8/Premissas!$F$42*BA5</f>
+        <f>BA8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BB9" s="12">
-        <f>BB8/Premissas!$F$42*BB5</f>
+        <f>BB8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BC9" s="12">
-        <f>BC8/Premissas!$F$42*BC5</f>
+        <f>BC8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BD9" s="12">
-        <f>BD8/Premissas!$F$42*BD5</f>
+        <f>BD8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BE9" s="12">
-        <f>BE8/Premissas!$F$42*BE5</f>
+        <f>BE8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BF9" s="12">
-        <f>BF8/Premissas!$F$42*BF5</f>
+        <f>BF8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BG9" s="12">
-        <f>BG8/Premissas!$F$42*BG5</f>
+        <f>BG8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BH9" s="12">
-        <f>BH8/Premissas!$F$42*BH5</f>
+        <f>BH8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BI9" s="12">
-        <f>BI8/Premissas!$F$42*BI5</f>
+        <f>BI8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BJ9" s="12">
-        <f>BJ8/Premissas!$F$42*BJ5</f>
+        <f>BJ8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BK9" s="12">
-        <f>BK8/Premissas!$F$42*BK5</f>
+        <f>BK8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BL9" s="12">
-        <f>BL8/Premissas!$F$42*BL5</f>
+        <f>BL8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BM9" s="12">
-        <f>BM8/Premissas!$F$42*BM5</f>
+        <f>BM8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BN9" s="12">
-        <f>BN8/Premissas!$F$42*BN5</f>
+        <f>BN8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BO9" s="12">
-        <f>BO8/Premissas!$F$42*BO5</f>
+        <f>BO8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BP9" s="12">
-        <f>BP8/Premissas!$F$42*BP5</f>
+        <f>BP8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BQ9" s="12">
-        <f>BQ8/Premissas!$F$42*BQ5</f>
+        <f>BQ8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BR9" s="12">
-        <f>BR8/Premissas!$F$42*BR5</f>
+        <f>BR8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BS9" s="12">
-        <f>BS8/Premissas!$F$42*BS5</f>
+        <f>BS8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BT9" s="12">
-        <f>BT8/Premissas!$F$42*BT5</f>
+        <f>BT8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BU9" s="12">
-        <f>BU8/Premissas!$F$42*BU5</f>
+        <f>BU8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BV9" s="12">
-        <f>BV8/Premissas!$F$42*BV5</f>
+        <f>BV8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BW9" s="12">
-        <f>BW8/Premissas!$F$42*BW5</f>
+        <f>BW8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BX9" s="12">
-        <f>BX8/Premissas!$F$42*BX5</f>
+        <f>BX8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BY9" s="12">
-        <f>BY8/Premissas!$F$42*BY5</f>
+        <f>BY8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="BZ9" s="12">
-        <f>BZ8/Premissas!$F$42*BZ5</f>
+        <f>BZ8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="CA9" s="12">
-        <f>CA8/Premissas!$F$42*CA5</f>
+        <f>CA8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="CB9" s="12">
-        <f>CB8/Premissas!$F$42*CB5</f>
+        <f>CB8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="CC9" s="12">
-        <f>CC8/Premissas!$F$42*CC5</f>
+        <f>CC8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="CD9" s="12">
-        <f>CD8/Premissas!$F$42*CD5</f>
+        <f>CD8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="CE9" s="12">
-        <f>CE8/Premissas!$F$42*CE5</f>
+        <f>CE8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="CF9" s="12">
-        <f>CF8/Premissas!$F$42*CF5</f>
+        <f>CF8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="CG9" s="12">
-        <f>CG8/Premissas!$F$42*CG5</f>
+        <f>CG8/Premissas!$F$42</f>
         <v/>
       </c>
       <c r="CH9" s="12">
-        <f>CH8/Premissas!$F$42*CH5</f>
+        <f>CH8/Premissas!$F$42</f>
         <v/>
       </c>
     </row>
@@ -17652,343 +17856,343 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Custo direto (IA, ferramentas, hospedagem)</t>
+          <t>Custo direto (IA, ferramentas, hospedagem, implantação)</t>
         </is>
       </c>
       <c r="C53" s="26">
-        <f>C18*Premissas!$F$49+C24*Premissas!$F$54+C30*Premissas!$F$59+C36*Premissas!$F$65</f>
+        <f>C18*Premissas!$F$49+C24*Premissas!$F$54+C30*Premissas!$F$59+C36*Premissas!$F$65+C12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="D53" s="26">
-        <f>D18*Premissas!$F$49+D24*Premissas!$F$54+D30*Premissas!$F$59+D36*Premissas!$F$65</f>
+        <f>D18*Premissas!$F$49+D24*Premissas!$F$54+D30*Premissas!$F$59+D36*Premissas!$F$65+D12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="E53" s="26">
-        <f>E18*Premissas!$F$49+E24*Premissas!$F$54+E30*Premissas!$F$59+E36*Premissas!$F$65</f>
+        <f>E18*Premissas!$F$49+E24*Premissas!$F$54+E30*Premissas!$F$59+E36*Premissas!$F$65+E12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="F53" s="26">
-        <f>F18*Premissas!$F$49+F24*Premissas!$F$54+F30*Premissas!$F$59+F36*Premissas!$F$65</f>
+        <f>F18*Premissas!$F$49+F24*Premissas!$F$54+F30*Premissas!$F$59+F36*Premissas!$F$65+F12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="G53" s="26">
-        <f>G18*Premissas!$F$49+G24*Premissas!$F$54+G30*Premissas!$F$59+G36*Premissas!$F$65</f>
+        <f>G18*Premissas!$F$49+G24*Premissas!$F$54+G30*Premissas!$F$59+G36*Premissas!$F$65+G12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="H53" s="26">
-        <f>H18*Premissas!$F$49+H24*Premissas!$F$54+H30*Premissas!$F$59+H36*Premissas!$F$65</f>
+        <f>H18*Premissas!$F$49+H24*Premissas!$F$54+H30*Premissas!$F$59+H36*Premissas!$F$65+H12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="I53" s="26">
-        <f>I18*Premissas!$F$49+I24*Premissas!$F$54+I30*Premissas!$F$59+I36*Premissas!$F$65</f>
+        <f>I18*Premissas!$F$49+I24*Premissas!$F$54+I30*Premissas!$F$59+I36*Premissas!$F$65+I12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="J53" s="26">
-        <f>J18*Premissas!$F$49+J24*Premissas!$F$54+J30*Premissas!$F$59+J36*Premissas!$F$65</f>
+        <f>J18*Premissas!$F$49+J24*Premissas!$F$54+J30*Premissas!$F$59+J36*Premissas!$F$65+J12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="K53" s="26">
-        <f>K18*Premissas!$F$49+K24*Premissas!$F$54+K30*Premissas!$F$59+K36*Premissas!$F$65</f>
+        <f>K18*Premissas!$F$49+K24*Premissas!$F$54+K30*Premissas!$F$59+K36*Premissas!$F$65+K12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="L53" s="26">
-        <f>L18*Premissas!$F$49+L24*Premissas!$F$54+L30*Premissas!$F$59+L36*Premissas!$F$65</f>
+        <f>L18*Premissas!$F$49+L24*Premissas!$F$54+L30*Premissas!$F$59+L36*Premissas!$F$65+L12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="M53" s="26">
-        <f>M18*Premissas!$F$49+M24*Premissas!$F$54+M30*Premissas!$F$59+M36*Premissas!$F$65</f>
+        <f>M18*Premissas!$F$49+M24*Premissas!$F$54+M30*Premissas!$F$59+M36*Premissas!$F$65+M12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="N53" s="26">
-        <f>N18*Premissas!$F$49+N24*Premissas!$F$54+N30*Premissas!$F$59+N36*Premissas!$F$65</f>
+        <f>N18*Premissas!$F$49+N24*Premissas!$F$54+N30*Premissas!$F$59+N36*Premissas!$F$65+N12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="O53" s="26">
-        <f>O18*Premissas!$F$49+O24*Premissas!$F$54+O30*Premissas!$F$59+O36*Premissas!$F$65</f>
+        <f>O18*Premissas!$F$49+O24*Premissas!$F$54+O30*Premissas!$F$59+O36*Premissas!$F$65+O12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="P53" s="26">
-        <f>P18*Premissas!$F$49+P24*Premissas!$F$54+P30*Premissas!$F$59+P36*Premissas!$F$65</f>
+        <f>P18*Premissas!$F$49+P24*Premissas!$F$54+P30*Premissas!$F$59+P36*Premissas!$F$65+P12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="Q53" s="26">
-        <f>Q18*Premissas!$F$49+Q24*Premissas!$F$54+Q30*Premissas!$F$59+Q36*Premissas!$F$65</f>
+        <f>Q18*Premissas!$F$49+Q24*Premissas!$F$54+Q30*Premissas!$F$59+Q36*Premissas!$F$65+Q12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="R53" s="26">
-        <f>R18*Premissas!$F$49+R24*Premissas!$F$54+R30*Premissas!$F$59+R36*Premissas!$F$65</f>
+        <f>R18*Premissas!$F$49+R24*Premissas!$F$54+R30*Premissas!$F$59+R36*Premissas!$F$65+R12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="S53" s="26">
-        <f>S18*Premissas!$F$49+S24*Premissas!$F$54+S30*Premissas!$F$59+S36*Premissas!$F$65</f>
+        <f>S18*Premissas!$F$49+S24*Premissas!$F$54+S30*Premissas!$F$59+S36*Premissas!$F$65+S12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="T53" s="26">
-        <f>T18*Premissas!$F$49+T24*Premissas!$F$54+T30*Premissas!$F$59+T36*Premissas!$F$65</f>
+        <f>T18*Premissas!$F$49+T24*Premissas!$F$54+T30*Premissas!$F$59+T36*Premissas!$F$65+T12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="U53" s="26">
-        <f>U18*Premissas!$F$49+U24*Premissas!$F$54+U30*Premissas!$F$59+U36*Premissas!$F$65</f>
+        <f>U18*Premissas!$F$49+U24*Premissas!$F$54+U30*Premissas!$F$59+U36*Premissas!$F$65+U12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="V53" s="26">
-        <f>V18*Premissas!$F$49+V24*Premissas!$F$54+V30*Premissas!$F$59+V36*Premissas!$F$65</f>
+        <f>V18*Premissas!$F$49+V24*Premissas!$F$54+V30*Premissas!$F$59+V36*Premissas!$F$65+V12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="W53" s="26">
-        <f>W18*Premissas!$F$49+W24*Premissas!$F$54+W30*Premissas!$F$59+W36*Premissas!$F$65</f>
+        <f>W18*Premissas!$F$49+W24*Premissas!$F$54+W30*Premissas!$F$59+W36*Premissas!$F$65+W12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="X53" s="26">
-        <f>X18*Premissas!$F$49+X24*Premissas!$F$54+X30*Premissas!$F$59+X36*Premissas!$F$65</f>
+        <f>X18*Premissas!$F$49+X24*Premissas!$F$54+X30*Premissas!$F$59+X36*Premissas!$F$65+X12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="Y53" s="26">
-        <f>Y18*Premissas!$F$49+Y24*Premissas!$F$54+Y30*Premissas!$F$59+Y36*Premissas!$F$65</f>
+        <f>Y18*Premissas!$F$49+Y24*Premissas!$F$54+Y30*Premissas!$F$59+Y36*Premissas!$F$65+Y12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="Z53" s="26">
-        <f>Z18*Premissas!$F$49+Z24*Premissas!$F$54+Z30*Premissas!$F$59+Z36*Premissas!$F$65</f>
+        <f>Z18*Premissas!$F$49+Z24*Premissas!$F$54+Z30*Premissas!$F$59+Z36*Premissas!$F$65+Z12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AA53" s="26">
-        <f>AA18*Premissas!$F$49+AA24*Premissas!$F$54+AA30*Premissas!$F$59+AA36*Premissas!$F$65</f>
+        <f>AA18*Premissas!$F$49+AA24*Premissas!$F$54+AA30*Premissas!$F$59+AA36*Premissas!$F$65+AA12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AB53" s="26">
-        <f>AB18*Premissas!$F$49+AB24*Premissas!$F$54+AB30*Premissas!$F$59+AB36*Premissas!$F$65</f>
+        <f>AB18*Premissas!$F$49+AB24*Premissas!$F$54+AB30*Premissas!$F$59+AB36*Premissas!$F$65+AB12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AC53" s="26">
-        <f>AC18*Premissas!$F$49+AC24*Premissas!$F$54+AC30*Premissas!$F$59+AC36*Premissas!$F$65</f>
+        <f>AC18*Premissas!$F$49+AC24*Premissas!$F$54+AC30*Premissas!$F$59+AC36*Premissas!$F$65+AC12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AD53" s="26">
-        <f>AD18*Premissas!$F$49+AD24*Premissas!$F$54+AD30*Premissas!$F$59+AD36*Premissas!$F$65</f>
+        <f>AD18*Premissas!$F$49+AD24*Premissas!$F$54+AD30*Premissas!$F$59+AD36*Premissas!$F$65+AD12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AE53" s="26">
-        <f>AE18*Premissas!$F$49+AE24*Premissas!$F$54+AE30*Premissas!$F$59+AE36*Premissas!$F$65</f>
+        <f>AE18*Premissas!$F$49+AE24*Premissas!$F$54+AE30*Premissas!$F$59+AE36*Premissas!$F$65+AE12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AF53" s="26">
-        <f>AF18*Premissas!$F$49+AF24*Premissas!$F$54+AF30*Premissas!$F$59+AF36*Premissas!$F$65</f>
+        <f>AF18*Premissas!$F$49+AF24*Premissas!$F$54+AF30*Premissas!$F$59+AF36*Premissas!$F$65+AF12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AG53" s="26">
-        <f>AG18*Premissas!$F$49+AG24*Premissas!$F$54+AG30*Premissas!$F$59+AG36*Premissas!$F$65</f>
+        <f>AG18*Premissas!$F$49+AG24*Premissas!$F$54+AG30*Premissas!$F$59+AG36*Premissas!$F$65+AG12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AH53" s="26">
-        <f>AH18*Premissas!$F$49+AH24*Premissas!$F$54+AH30*Premissas!$F$59+AH36*Premissas!$F$65</f>
+        <f>AH18*Premissas!$F$49+AH24*Premissas!$F$54+AH30*Premissas!$F$59+AH36*Premissas!$F$65+AH12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AI53" s="26">
-        <f>AI18*Premissas!$F$49+AI24*Premissas!$F$54+AI30*Premissas!$F$59+AI36*Premissas!$F$65</f>
+        <f>AI18*Premissas!$F$49+AI24*Premissas!$F$54+AI30*Premissas!$F$59+AI36*Premissas!$F$65+AI12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AJ53" s="26">
-        <f>AJ18*Premissas!$F$49+AJ24*Premissas!$F$54+AJ30*Premissas!$F$59+AJ36*Premissas!$F$65</f>
+        <f>AJ18*Premissas!$F$49+AJ24*Premissas!$F$54+AJ30*Premissas!$F$59+AJ36*Premissas!$F$65+AJ12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AK53" s="26">
-        <f>AK18*Premissas!$F$49+AK24*Premissas!$F$54+AK30*Premissas!$F$59+AK36*Premissas!$F$65</f>
+        <f>AK18*Premissas!$F$49+AK24*Premissas!$F$54+AK30*Premissas!$F$59+AK36*Premissas!$F$65+AK12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AL53" s="26">
-        <f>AL18*Premissas!$F$49+AL24*Premissas!$F$54+AL30*Premissas!$F$59+AL36*Premissas!$F$65</f>
+        <f>AL18*Premissas!$F$49+AL24*Premissas!$F$54+AL30*Premissas!$F$59+AL36*Premissas!$F$65+AL12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AM53" s="26">
-        <f>AM18*Premissas!$F$49+AM24*Premissas!$F$54+AM30*Premissas!$F$59+AM36*Premissas!$F$65</f>
+        <f>AM18*Premissas!$F$49+AM24*Premissas!$F$54+AM30*Premissas!$F$59+AM36*Premissas!$F$65+AM12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AN53" s="26">
-        <f>AN18*Premissas!$F$49+AN24*Premissas!$F$54+AN30*Premissas!$F$59+AN36*Premissas!$F$65</f>
+        <f>AN18*Premissas!$F$49+AN24*Premissas!$F$54+AN30*Premissas!$F$59+AN36*Premissas!$F$65+AN12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AO53" s="26">
-        <f>AO18*Premissas!$F$49+AO24*Premissas!$F$54+AO30*Premissas!$F$59+AO36*Premissas!$F$65</f>
+        <f>AO18*Premissas!$F$49+AO24*Premissas!$F$54+AO30*Premissas!$F$59+AO36*Premissas!$F$65+AO12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AP53" s="26">
-        <f>AP18*Premissas!$F$49+AP24*Premissas!$F$54+AP30*Premissas!$F$59+AP36*Premissas!$F$65</f>
+        <f>AP18*Premissas!$F$49+AP24*Premissas!$F$54+AP30*Premissas!$F$59+AP36*Premissas!$F$65+AP12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AQ53" s="26">
-        <f>AQ18*Premissas!$F$49+AQ24*Premissas!$F$54+AQ30*Premissas!$F$59+AQ36*Premissas!$F$65</f>
+        <f>AQ18*Premissas!$F$49+AQ24*Premissas!$F$54+AQ30*Premissas!$F$59+AQ36*Premissas!$F$65+AQ12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AR53" s="26">
-        <f>AR18*Premissas!$F$49+AR24*Premissas!$F$54+AR30*Premissas!$F$59+AR36*Premissas!$F$65</f>
+        <f>AR18*Premissas!$F$49+AR24*Premissas!$F$54+AR30*Premissas!$F$59+AR36*Premissas!$F$65+AR12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AS53" s="26">
-        <f>AS18*Premissas!$F$49+AS24*Premissas!$F$54+AS30*Premissas!$F$59+AS36*Premissas!$F$65</f>
+        <f>AS18*Premissas!$F$49+AS24*Premissas!$F$54+AS30*Premissas!$F$59+AS36*Premissas!$F$65+AS12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AT53" s="26">
-        <f>AT18*Premissas!$F$49+AT24*Premissas!$F$54+AT30*Premissas!$F$59+AT36*Premissas!$F$65</f>
+        <f>AT18*Premissas!$F$49+AT24*Premissas!$F$54+AT30*Premissas!$F$59+AT36*Premissas!$F$65+AT12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AU53" s="26">
-        <f>AU18*Premissas!$F$49+AU24*Premissas!$F$54+AU30*Premissas!$F$59+AU36*Premissas!$F$65</f>
+        <f>AU18*Premissas!$F$49+AU24*Premissas!$F$54+AU30*Premissas!$F$59+AU36*Premissas!$F$65+AU12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AV53" s="26">
-        <f>AV18*Premissas!$F$49+AV24*Premissas!$F$54+AV30*Premissas!$F$59+AV36*Premissas!$F$65</f>
+        <f>AV18*Premissas!$F$49+AV24*Premissas!$F$54+AV30*Premissas!$F$59+AV36*Premissas!$F$65+AV12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AW53" s="26">
-        <f>AW18*Premissas!$F$49+AW24*Premissas!$F$54+AW30*Premissas!$F$59+AW36*Premissas!$F$65</f>
+        <f>AW18*Premissas!$F$49+AW24*Premissas!$F$54+AW30*Premissas!$F$59+AW36*Premissas!$F$65+AW12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AX53" s="26">
-        <f>AX18*Premissas!$F$49+AX24*Premissas!$F$54+AX30*Premissas!$F$59+AX36*Premissas!$F$65</f>
+        <f>AX18*Premissas!$F$49+AX24*Premissas!$F$54+AX30*Premissas!$F$59+AX36*Premissas!$F$65+AX12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AY53" s="26">
-        <f>AY18*Premissas!$F$49+AY24*Premissas!$F$54+AY30*Premissas!$F$59+AY36*Premissas!$F$65</f>
+        <f>AY18*Premissas!$F$49+AY24*Premissas!$F$54+AY30*Premissas!$F$59+AY36*Premissas!$F$65+AY12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="AZ53" s="26">
-        <f>AZ18*Premissas!$F$49+AZ24*Premissas!$F$54+AZ30*Premissas!$F$59+AZ36*Premissas!$F$65</f>
+        <f>AZ18*Premissas!$F$49+AZ24*Premissas!$F$54+AZ30*Premissas!$F$59+AZ36*Premissas!$F$65+AZ12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BA53" s="26">
-        <f>BA18*Premissas!$F$49+BA24*Premissas!$F$54+BA30*Premissas!$F$59+BA36*Premissas!$F$65</f>
+        <f>BA18*Premissas!$F$49+BA24*Premissas!$F$54+BA30*Premissas!$F$59+BA36*Premissas!$F$65+BA12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BB53" s="26">
-        <f>BB18*Premissas!$F$49+BB24*Premissas!$F$54+BB30*Premissas!$F$59+BB36*Premissas!$F$65</f>
+        <f>BB18*Premissas!$F$49+BB24*Premissas!$F$54+BB30*Premissas!$F$59+BB36*Premissas!$F$65+BB12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BC53" s="26">
-        <f>BC18*Premissas!$F$49+BC24*Premissas!$F$54+BC30*Premissas!$F$59+BC36*Premissas!$F$65</f>
+        <f>BC18*Premissas!$F$49+BC24*Premissas!$F$54+BC30*Premissas!$F$59+BC36*Premissas!$F$65+BC12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BD53" s="26">
-        <f>BD18*Premissas!$F$49+BD24*Premissas!$F$54+BD30*Premissas!$F$59+BD36*Premissas!$F$65</f>
+        <f>BD18*Premissas!$F$49+BD24*Premissas!$F$54+BD30*Premissas!$F$59+BD36*Premissas!$F$65+BD12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BE53" s="26">
-        <f>BE18*Premissas!$F$49+BE24*Premissas!$F$54+BE30*Premissas!$F$59+BE36*Premissas!$F$65</f>
+        <f>BE18*Premissas!$F$49+BE24*Premissas!$F$54+BE30*Premissas!$F$59+BE36*Premissas!$F$65+BE12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BF53" s="26">
-        <f>BF18*Premissas!$F$49+BF24*Premissas!$F$54+BF30*Premissas!$F$59+BF36*Premissas!$F$65</f>
+        <f>BF18*Premissas!$F$49+BF24*Premissas!$F$54+BF30*Premissas!$F$59+BF36*Premissas!$F$65+BF12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BG53" s="26">
-        <f>BG18*Premissas!$F$49+BG24*Premissas!$F$54+BG30*Premissas!$F$59+BG36*Premissas!$F$65</f>
+        <f>BG18*Premissas!$F$49+BG24*Premissas!$F$54+BG30*Premissas!$F$59+BG36*Premissas!$F$65+BG12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BH53" s="26">
-        <f>BH18*Premissas!$F$49+BH24*Premissas!$F$54+BH30*Premissas!$F$59+BH36*Premissas!$F$65</f>
+        <f>BH18*Premissas!$F$49+BH24*Premissas!$F$54+BH30*Premissas!$F$59+BH36*Premissas!$F$65+BH12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BI53" s="26">
-        <f>BI18*Premissas!$F$49+BI24*Premissas!$F$54+BI30*Premissas!$F$59+BI36*Premissas!$F$65</f>
+        <f>BI18*Premissas!$F$49+BI24*Premissas!$F$54+BI30*Premissas!$F$59+BI36*Premissas!$F$65+BI12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BJ53" s="26">
-        <f>BJ18*Premissas!$F$49+BJ24*Premissas!$F$54+BJ30*Premissas!$F$59+BJ36*Premissas!$F$65</f>
+        <f>BJ18*Premissas!$F$49+BJ24*Premissas!$F$54+BJ30*Premissas!$F$59+BJ36*Premissas!$F$65+BJ12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BK53" s="26">
-        <f>BK18*Premissas!$F$49+BK24*Premissas!$F$54+BK30*Premissas!$F$59+BK36*Premissas!$F$65</f>
+        <f>BK18*Premissas!$F$49+BK24*Premissas!$F$54+BK30*Premissas!$F$59+BK36*Premissas!$F$65+BK12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BL53" s="26">
-        <f>BL18*Premissas!$F$49+BL24*Premissas!$F$54+BL30*Premissas!$F$59+BL36*Premissas!$F$65</f>
+        <f>BL18*Premissas!$F$49+BL24*Premissas!$F$54+BL30*Premissas!$F$59+BL36*Premissas!$F$65+BL12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BM53" s="26">
-        <f>BM18*Premissas!$F$49+BM24*Premissas!$F$54+BM30*Premissas!$F$59+BM36*Premissas!$F$65</f>
+        <f>BM18*Premissas!$F$49+BM24*Premissas!$F$54+BM30*Premissas!$F$59+BM36*Premissas!$F$65+BM12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BN53" s="26">
-        <f>BN18*Premissas!$F$49+BN24*Premissas!$F$54+BN30*Premissas!$F$59+BN36*Premissas!$F$65</f>
+        <f>BN18*Premissas!$F$49+BN24*Premissas!$F$54+BN30*Premissas!$F$59+BN36*Premissas!$F$65+BN12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BO53" s="26">
-        <f>BO18*Premissas!$F$49+BO24*Premissas!$F$54+BO30*Premissas!$F$59+BO36*Premissas!$F$65</f>
+        <f>BO18*Premissas!$F$49+BO24*Premissas!$F$54+BO30*Premissas!$F$59+BO36*Premissas!$F$65+BO12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BP53" s="26">
-        <f>BP18*Premissas!$F$49+BP24*Premissas!$F$54+BP30*Premissas!$F$59+BP36*Premissas!$F$65</f>
+        <f>BP18*Premissas!$F$49+BP24*Premissas!$F$54+BP30*Premissas!$F$59+BP36*Premissas!$F$65+BP12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BQ53" s="26">
-        <f>BQ18*Premissas!$F$49+BQ24*Premissas!$F$54+BQ30*Premissas!$F$59+BQ36*Premissas!$F$65</f>
+        <f>BQ18*Premissas!$F$49+BQ24*Premissas!$F$54+BQ30*Premissas!$F$59+BQ36*Premissas!$F$65+BQ12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BR53" s="26">
-        <f>BR18*Premissas!$F$49+BR24*Premissas!$F$54+BR30*Premissas!$F$59+BR36*Premissas!$F$65</f>
+        <f>BR18*Premissas!$F$49+BR24*Premissas!$F$54+BR30*Premissas!$F$59+BR36*Premissas!$F$65+BR12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BS53" s="26">
-        <f>BS18*Premissas!$F$49+BS24*Premissas!$F$54+BS30*Premissas!$F$59+BS36*Premissas!$F$65</f>
+        <f>BS18*Premissas!$F$49+BS24*Premissas!$F$54+BS30*Premissas!$F$59+BS36*Premissas!$F$65+BS12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BT53" s="26">
-        <f>BT18*Premissas!$F$49+BT24*Premissas!$F$54+BT30*Premissas!$F$59+BT36*Premissas!$F$65</f>
+        <f>BT18*Premissas!$F$49+BT24*Premissas!$F$54+BT30*Premissas!$F$59+BT36*Premissas!$F$65+BT12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BU53" s="26">
-        <f>BU18*Premissas!$F$49+BU24*Premissas!$F$54+BU30*Premissas!$F$59+BU36*Premissas!$F$65</f>
+        <f>BU18*Premissas!$F$49+BU24*Premissas!$F$54+BU30*Premissas!$F$59+BU36*Premissas!$F$65+BU12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BV53" s="26">
-        <f>BV18*Premissas!$F$49+BV24*Premissas!$F$54+BV30*Premissas!$F$59+BV36*Premissas!$F$65</f>
+        <f>BV18*Premissas!$F$49+BV24*Premissas!$F$54+BV30*Premissas!$F$59+BV36*Premissas!$F$65+BV12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BW53" s="26">
-        <f>BW18*Premissas!$F$49+BW24*Premissas!$F$54+BW30*Premissas!$F$59+BW36*Premissas!$F$65</f>
+        <f>BW18*Premissas!$F$49+BW24*Premissas!$F$54+BW30*Premissas!$F$59+BW36*Premissas!$F$65+BW12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BX53" s="26">
-        <f>BX18*Premissas!$F$49+BX24*Premissas!$F$54+BX30*Premissas!$F$59+BX36*Premissas!$F$65</f>
+        <f>BX18*Premissas!$F$49+BX24*Premissas!$F$54+BX30*Premissas!$F$59+BX36*Premissas!$F$65+BX12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BY53" s="26">
-        <f>BY18*Premissas!$F$49+BY24*Premissas!$F$54+BY30*Premissas!$F$59+BY36*Premissas!$F$65</f>
+        <f>BY18*Premissas!$F$49+BY24*Premissas!$F$54+BY30*Premissas!$F$59+BY36*Premissas!$F$65+BY12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="BZ53" s="26">
-        <f>BZ18*Premissas!$F$49+BZ24*Premissas!$F$54+BZ30*Premissas!$F$59+BZ36*Premissas!$F$65</f>
+        <f>BZ18*Premissas!$F$49+BZ24*Premissas!$F$54+BZ30*Premissas!$F$59+BZ36*Premissas!$F$65+BZ12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="CA53" s="26">
-        <f>CA18*Premissas!$F$49+CA24*Premissas!$F$54+CA30*Premissas!$F$59+CA36*Premissas!$F$65</f>
+        <f>CA18*Premissas!$F$49+CA24*Premissas!$F$54+CA30*Premissas!$F$59+CA36*Premissas!$F$65+CA12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="CB53" s="26">
-        <f>CB18*Premissas!$F$49+CB24*Premissas!$F$54+CB30*Premissas!$F$59+CB36*Premissas!$F$65</f>
+        <f>CB18*Premissas!$F$49+CB24*Premissas!$F$54+CB30*Premissas!$F$59+CB36*Premissas!$F$65+CB12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="CC53" s="26">
-        <f>CC18*Premissas!$F$49+CC24*Premissas!$F$54+CC30*Premissas!$F$59+CC36*Premissas!$F$65</f>
+        <f>CC18*Premissas!$F$49+CC24*Premissas!$F$54+CC30*Premissas!$F$59+CC36*Premissas!$F$65+CC12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="CD53" s="26">
-        <f>CD18*Premissas!$F$49+CD24*Premissas!$F$54+CD30*Premissas!$F$59+CD36*Premissas!$F$65</f>
+        <f>CD18*Premissas!$F$49+CD24*Premissas!$F$54+CD30*Premissas!$F$59+CD36*Premissas!$F$65+CD12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="CE53" s="26">
-        <f>CE18*Premissas!$F$49+CE24*Premissas!$F$54+CE30*Premissas!$F$59+CE36*Premissas!$F$65</f>
+        <f>CE18*Premissas!$F$49+CE24*Premissas!$F$54+CE30*Premissas!$F$59+CE36*Premissas!$F$65+CE12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="CF53" s="26">
-        <f>CF18*Premissas!$F$49+CF24*Premissas!$F$54+CF30*Premissas!$F$59+CF36*Premissas!$F$65</f>
+        <f>CF18*Premissas!$F$49+CF24*Premissas!$F$54+CF30*Premissas!$F$59+CF36*Premissas!$F$65+CF12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="CG53" s="26">
-        <f>CG18*Premissas!$F$49+CG24*Premissas!$F$54+CG30*Premissas!$F$59+CG36*Premissas!$F$65</f>
+        <f>CG18*Premissas!$F$49+CG24*Premissas!$F$54+CG30*Premissas!$F$59+CG36*Premissas!$F$65+CG12*Premissas!$F$105</f>
         <v/>
       </c>
       <c r="CH53" s="26">
-        <f>CH18*Premissas!$F$49+CH24*Premissas!$F$54+CH30*Premissas!$F$59+CH36*Premissas!$F$65</f>
+        <f>CH18*Premissas!$F$49+CH24*Premissas!$F$54+CH30*Premissas!$F$59+CH36*Premissas!$F$65+CH12*Premissas!$F$105</f>
         <v/>
       </c>
     </row>
@@ -21433,343 +21637,343 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Comissões de parceria</t>
+          <t>Comissões de parceria e meses grátis de indicação</t>
         </is>
       </c>
       <c r="C66" s="26">
-        <f>C10*Premissas!$F$43</f>
+        <f>C10*Premissas!$F$43+C11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="D66" s="26">
-        <f>D10*Premissas!$F$43</f>
+        <f>D10*Premissas!$F$43+D11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="E66" s="26">
-        <f>E10*Premissas!$F$43</f>
+        <f>E10*Premissas!$F$43+E11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="F66" s="26">
-        <f>F10*Premissas!$F$43</f>
+        <f>F10*Premissas!$F$43+F11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="G66" s="26">
-        <f>G10*Premissas!$F$43</f>
+        <f>G10*Premissas!$F$43+G11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="H66" s="26">
-        <f>H10*Premissas!$F$43</f>
+        <f>H10*Premissas!$F$43+H11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="I66" s="26">
-        <f>I10*Premissas!$F$43</f>
+        <f>I10*Premissas!$F$43+I11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="J66" s="26">
-        <f>J10*Premissas!$F$43</f>
+        <f>J10*Premissas!$F$43+J11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="K66" s="26">
-        <f>K10*Premissas!$F$43</f>
+        <f>K10*Premissas!$F$43+K11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="L66" s="26">
-        <f>L10*Premissas!$F$43</f>
+        <f>L10*Premissas!$F$43+L11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="M66" s="26">
-        <f>M10*Premissas!$F$43</f>
+        <f>M10*Premissas!$F$43+M11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="N66" s="26">
-        <f>N10*Premissas!$F$43</f>
+        <f>N10*Premissas!$F$43+N11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="O66" s="26">
-        <f>O10*Premissas!$F$43</f>
+        <f>O10*Premissas!$F$43+O11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="P66" s="26">
-        <f>P10*Premissas!$F$43</f>
+        <f>P10*Premissas!$F$43+P11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="Q66" s="26">
-        <f>Q10*Premissas!$F$43</f>
+        <f>Q10*Premissas!$F$43+Q11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="R66" s="26">
-        <f>R10*Premissas!$F$43</f>
+        <f>R10*Premissas!$F$43+R11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="S66" s="26">
-        <f>S10*Premissas!$F$43</f>
+        <f>S10*Premissas!$F$43+S11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="T66" s="26">
-        <f>T10*Premissas!$F$43</f>
+        <f>T10*Premissas!$F$43+T11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="U66" s="26">
-        <f>U10*Premissas!$F$43</f>
+        <f>U10*Premissas!$F$43+U11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="V66" s="26">
-        <f>V10*Premissas!$F$43</f>
+        <f>V10*Premissas!$F$43+V11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="W66" s="26">
-        <f>W10*Premissas!$F$43</f>
+        <f>W10*Premissas!$F$43+W11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="X66" s="26">
-        <f>X10*Premissas!$F$43</f>
+        <f>X10*Premissas!$F$43+X11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="Y66" s="26">
-        <f>Y10*Premissas!$F$43</f>
+        <f>Y10*Premissas!$F$43+Y11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="Z66" s="26">
-        <f>Z10*Premissas!$F$43</f>
+        <f>Z10*Premissas!$F$43+Z11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AA66" s="26">
-        <f>AA10*Premissas!$F$43</f>
+        <f>AA10*Premissas!$F$43+AA11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AB66" s="26">
-        <f>AB10*Premissas!$F$43</f>
+        <f>AB10*Premissas!$F$43+AB11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AC66" s="26">
-        <f>AC10*Premissas!$F$43</f>
+        <f>AC10*Premissas!$F$43+AC11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AD66" s="26">
-        <f>AD10*Premissas!$F$43</f>
+        <f>AD10*Premissas!$F$43+AD11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AE66" s="26">
-        <f>AE10*Premissas!$F$43</f>
+        <f>AE10*Premissas!$F$43+AE11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AF66" s="26">
-        <f>AF10*Premissas!$F$43</f>
+        <f>AF10*Premissas!$F$43+AF11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AG66" s="26">
-        <f>AG10*Premissas!$F$43</f>
+        <f>AG10*Premissas!$F$43+AG11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AH66" s="26">
-        <f>AH10*Premissas!$F$43</f>
+        <f>AH10*Premissas!$F$43+AH11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AI66" s="26">
-        <f>AI10*Premissas!$F$43</f>
+        <f>AI10*Premissas!$F$43+AI11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AJ66" s="26">
-        <f>AJ10*Premissas!$F$43</f>
+        <f>AJ10*Premissas!$F$43+AJ11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AK66" s="26">
-        <f>AK10*Premissas!$F$43</f>
+        <f>AK10*Premissas!$F$43+AK11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AL66" s="26">
-        <f>AL10*Premissas!$F$43</f>
+        <f>AL10*Premissas!$F$43+AL11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AM66" s="26">
-        <f>AM10*Premissas!$F$43</f>
+        <f>AM10*Premissas!$F$43+AM11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AN66" s="26">
-        <f>AN10*Premissas!$F$43</f>
+        <f>AN10*Premissas!$F$43+AN11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AO66" s="26">
-        <f>AO10*Premissas!$F$43</f>
+        <f>AO10*Premissas!$F$43+AO11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AP66" s="26">
-        <f>AP10*Premissas!$F$43</f>
+        <f>AP10*Premissas!$F$43+AP11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AQ66" s="26">
-        <f>AQ10*Premissas!$F$43</f>
+        <f>AQ10*Premissas!$F$43+AQ11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AR66" s="26">
-        <f>AR10*Premissas!$F$43</f>
+        <f>AR10*Premissas!$F$43+AR11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AS66" s="26">
-        <f>AS10*Premissas!$F$43</f>
+        <f>AS10*Premissas!$F$43+AS11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AT66" s="26">
-        <f>AT10*Premissas!$F$43</f>
+        <f>AT10*Premissas!$F$43+AT11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AU66" s="26">
-        <f>AU10*Premissas!$F$43</f>
+        <f>AU10*Premissas!$F$43+AU11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AV66" s="26">
-        <f>AV10*Premissas!$F$43</f>
+        <f>AV10*Premissas!$F$43+AV11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AW66" s="26">
-        <f>AW10*Premissas!$F$43</f>
+        <f>AW10*Premissas!$F$43+AW11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AX66" s="26">
-        <f>AX10*Premissas!$F$43</f>
+        <f>AX10*Premissas!$F$43+AX11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AY66" s="26">
-        <f>AY10*Premissas!$F$43</f>
+        <f>AY10*Premissas!$F$43+AY11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="AZ66" s="26">
-        <f>AZ10*Premissas!$F$43</f>
+        <f>AZ10*Premissas!$F$43+AZ11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BA66" s="26">
-        <f>BA10*Premissas!$F$43</f>
+        <f>BA10*Premissas!$F$43+BA11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BB66" s="26">
-        <f>BB10*Premissas!$F$43</f>
+        <f>BB10*Premissas!$F$43+BB11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BC66" s="26">
-        <f>BC10*Premissas!$F$43</f>
+        <f>BC10*Premissas!$F$43+BC11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BD66" s="26">
-        <f>BD10*Premissas!$F$43</f>
+        <f>BD10*Premissas!$F$43+BD11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BE66" s="26">
-        <f>BE10*Premissas!$F$43</f>
+        <f>BE10*Premissas!$F$43+BE11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BF66" s="26">
-        <f>BF10*Premissas!$F$43</f>
+        <f>BF10*Premissas!$F$43+BF11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BG66" s="26">
-        <f>BG10*Premissas!$F$43</f>
+        <f>BG10*Premissas!$F$43+BG11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BH66" s="26">
-        <f>BH10*Premissas!$F$43</f>
+        <f>BH10*Premissas!$F$43+BH11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BI66" s="26">
-        <f>BI10*Premissas!$F$43</f>
+        <f>BI10*Premissas!$F$43+BI11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BJ66" s="26">
-        <f>BJ10*Premissas!$F$43</f>
+        <f>BJ10*Premissas!$F$43+BJ11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BK66" s="26">
-        <f>BK10*Premissas!$F$43</f>
+        <f>BK10*Premissas!$F$43+BK11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BL66" s="26">
-        <f>BL10*Premissas!$F$43</f>
+        <f>BL10*Premissas!$F$43+BL11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BM66" s="26">
-        <f>BM10*Premissas!$F$43</f>
+        <f>BM10*Premissas!$F$43+BM11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BN66" s="26">
-        <f>BN10*Premissas!$F$43</f>
+        <f>BN10*Premissas!$F$43+BN11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BO66" s="26">
-        <f>BO10*Premissas!$F$43</f>
+        <f>BO10*Premissas!$F$43+BO11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BP66" s="26">
-        <f>BP10*Premissas!$F$43</f>
+        <f>BP10*Premissas!$F$43+BP11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BQ66" s="26">
-        <f>BQ10*Premissas!$F$43</f>
+        <f>BQ10*Premissas!$F$43+BQ11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BR66" s="26">
-        <f>BR10*Premissas!$F$43</f>
+        <f>BR10*Premissas!$F$43+BR11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BS66" s="26">
-        <f>BS10*Premissas!$F$43</f>
+        <f>BS10*Premissas!$F$43+BS11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BT66" s="26">
-        <f>BT10*Premissas!$F$43</f>
+        <f>BT10*Premissas!$F$43+BT11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BU66" s="26">
-        <f>BU10*Premissas!$F$43</f>
+        <f>BU10*Premissas!$F$43+BU11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BV66" s="26">
-        <f>BV10*Premissas!$F$43</f>
+        <f>BV10*Premissas!$F$43+BV11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BW66" s="26">
-        <f>BW10*Premissas!$F$43</f>
+        <f>BW10*Premissas!$F$43+BW11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BX66" s="26">
-        <f>BX10*Premissas!$F$43</f>
+        <f>BX10*Premissas!$F$43+BX11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BY66" s="26">
-        <f>BY10*Premissas!$F$43</f>
+        <f>BY10*Premissas!$F$43+BY11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="BZ66" s="26">
-        <f>BZ10*Premissas!$F$43</f>
+        <f>BZ10*Premissas!$F$43+BZ11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="CA66" s="26">
-        <f>CA10*Premissas!$F$43</f>
+        <f>CA10*Premissas!$F$43+CA11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="CB66" s="26">
-        <f>CB10*Premissas!$F$43</f>
+        <f>CB10*Premissas!$F$43+CB11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="CC66" s="26">
-        <f>CC10*Premissas!$F$43</f>
+        <f>CC10*Premissas!$F$43+CC11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="CD66" s="26">
-        <f>CD10*Premissas!$F$43</f>
+        <f>CD10*Premissas!$F$43+CD11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="CE66" s="26">
-        <f>CE10*Premissas!$F$43</f>
+        <f>CE10*Premissas!$F$43+CE11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="CF66" s="26">
-        <f>CF10*Premissas!$F$43</f>
+        <f>CF10*Premissas!$F$43+CF11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="CG66" s="26">
-        <f>CG10*Premissas!$F$43</f>
+        <f>CG10*Premissas!$F$43+CG11*Premissas!$F$107</f>
         <v/>
       </c>
       <c r="CH66" s="26">
-        <f>CH10*Premissas!$F$43</f>
+        <f>CH10*Premissas!$F$43+CH11*Premissas!$F$107</f>
         <v/>
       </c>
     </row>
@@ -26280,339 +26484,339 @@
         </is>
       </c>
       <c r="C8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,C3)*C4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,C3)*C4*C5</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,D3)*D4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,D3)*D4*D5</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,E3)*E4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,E3)*E4*E5</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,F3)*F4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,F3)*F4*F5</f>
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,G3)*G4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,G3)*G4*G5</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,H3)*H4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,H3)*H4*H5</f>
         <v/>
       </c>
       <c r="I8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,I3)*I4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,I3)*I4*I5</f>
         <v/>
       </c>
       <c r="J8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,J3)*J4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,J3)*J4*J5</f>
         <v/>
       </c>
       <c r="K8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,K3)*K4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,K3)*K4*K5</f>
         <v/>
       </c>
       <c r="L8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,L3)*L4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,L3)*L4*L5</f>
         <v/>
       </c>
       <c r="M8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,M3)*M4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,M3)*M4*M5</f>
         <v/>
       </c>
       <c r="N8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,N3)*N4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,N3)*N4*N5</f>
         <v/>
       </c>
       <c r="O8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,O3)*O4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,O3)*O4*O5</f>
         <v/>
       </c>
       <c r="P8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,P3)*P4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,P3)*P4*P5</f>
         <v/>
       </c>
       <c r="Q8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,Q3)*Q4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,Q3)*Q4*Q5</f>
         <v/>
       </c>
       <c r="R8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,R3)*R4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,R3)*R4*R5</f>
         <v/>
       </c>
       <c r="S8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,S3)*S4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,S3)*S4*S5</f>
         <v/>
       </c>
       <c r="T8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,T3)*T4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,T3)*T4*T5</f>
         <v/>
       </c>
       <c r="U8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,U3)*U4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,U3)*U4*U5</f>
         <v/>
       </c>
       <c r="V8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,V3)*V4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,V3)*V4*V5</f>
         <v/>
       </c>
       <c r="W8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,W3)*W4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,W3)*W4*W5</f>
         <v/>
       </c>
       <c r="X8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,X3)*X4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,X3)*X4*X5</f>
         <v/>
       </c>
       <c r="Y8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,Y3)*Y4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,Y3)*Y4*Y5</f>
         <v/>
       </c>
       <c r="Z8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,Z3)*Z4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,Z3)*Z4*Z5</f>
         <v/>
       </c>
       <c r="AA8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AA3)*AA4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AA3)*AA4*AA5</f>
         <v/>
       </c>
       <c r="AB8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AB3)*AB4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AB3)*AB4*AB5</f>
         <v/>
       </c>
       <c r="AC8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AC3)*AC4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AC3)*AC4*AC5</f>
         <v/>
       </c>
       <c r="AD8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AD3)*AD4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AD3)*AD4*AD5</f>
         <v/>
       </c>
       <c r="AE8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AE3)*AE4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AE3)*AE4*AE5</f>
         <v/>
       </c>
       <c r="AF8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AF3)*AF4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AF3)*AF4*AF5</f>
         <v/>
       </c>
       <c r="AG8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AG3)*AG4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AG3)*AG4*AG5</f>
         <v/>
       </c>
       <c r="AH8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AH3)*AH4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AH3)*AH4*AH5</f>
         <v/>
       </c>
       <c r="AI8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AI3)*AI4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AI3)*AI4*AI5</f>
         <v/>
       </c>
       <c r="AJ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AJ3)*AJ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AJ3)*AJ4*AJ5</f>
         <v/>
       </c>
       <c r="AK8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AK3)*AK4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AK3)*AK4*AK5</f>
         <v/>
       </c>
       <c r="AL8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AL3)*AL4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AL3)*AL4*AL5</f>
         <v/>
       </c>
       <c r="AM8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AM3)*AM4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AM3)*AM4*AM5</f>
         <v/>
       </c>
       <c r="AN8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AN3)*AN4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AN3)*AN4*AN5</f>
         <v/>
       </c>
       <c r="AO8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AO3)*AO4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AO3)*AO4*AO5</f>
         <v/>
       </c>
       <c r="AP8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AP3)*AP4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AP3)*AP4*AP5</f>
         <v/>
       </c>
       <c r="AQ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AQ3)*AQ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AQ3)*AQ4*AQ5</f>
         <v/>
       </c>
       <c r="AR8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AR3)*AR4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AR3)*AR4*AR5</f>
         <v/>
       </c>
       <c r="AS8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AS3)*AS4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AS3)*AS4*AS5</f>
         <v/>
       </c>
       <c r="AT8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AT3)*AT4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AT3)*AT4*AT5</f>
         <v/>
       </c>
       <c r="AU8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AU3)*AU4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AU3)*AU4*AU5</f>
         <v/>
       </c>
       <c r="AV8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AV3)*AV4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AV3)*AV4*AV5</f>
         <v/>
       </c>
       <c r="AW8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AW3)*AW4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AW3)*AW4*AW5</f>
         <v/>
       </c>
       <c r="AX8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AX3)*AX4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AX3)*AX4*AX5</f>
         <v/>
       </c>
       <c r="AY8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AY3)*AY4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AY3)*AY4*AY5</f>
         <v/>
       </c>
       <c r="AZ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,AZ3)*AZ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,AZ3)*AZ4*AZ5</f>
         <v/>
       </c>
       <c r="BA8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BA3)*BA4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BA3)*BA4*BA5</f>
         <v/>
       </c>
       <c r="BB8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BB3)*BB4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BB3)*BB4*BB5</f>
         <v/>
       </c>
       <c r="BC8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BC3)*BC4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BC3)*BC4*BC5</f>
         <v/>
       </c>
       <c r="BD8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BD3)*BD4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BD3)*BD4*BD5</f>
         <v/>
       </c>
       <c r="BE8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BE3)*BE4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BE3)*BE4*BE5</f>
         <v/>
       </c>
       <c r="BF8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BF3)*BF4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BF3)*BF4*BF5</f>
         <v/>
       </c>
       <c r="BG8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BG3)*BG4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BG3)*BG4*BG5</f>
         <v/>
       </c>
       <c r="BH8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BH3)*BH4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BH3)*BH4*BH5</f>
         <v/>
       </c>
       <c r="BI8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BI3)*BI4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BI3)*BI4*BI5</f>
         <v/>
       </c>
       <c r="BJ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BJ3)*BJ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BJ3)*BJ4*BJ5</f>
         <v/>
       </c>
       <c r="BK8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BK3)*BK4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BK3)*BK4*BK5</f>
         <v/>
       </c>
       <c r="BL8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BL3)*BL4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BL3)*BL4*BL5</f>
         <v/>
       </c>
       <c r="BM8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BM3)*BM4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BM3)*BM4*BM5</f>
         <v/>
       </c>
       <c r="BN8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BN3)*BN4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BN3)*BN4*BN5</f>
         <v/>
       </c>
       <c r="BO8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BO3)*BO4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BO3)*BO4*BO5</f>
         <v/>
       </c>
       <c r="BP8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BP3)*BP4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BP3)*BP4*BP5</f>
         <v/>
       </c>
       <c r="BQ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BQ3)*BQ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BQ3)*BQ4*BQ5</f>
         <v/>
       </c>
       <c r="BR8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BR3)*BR4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BR3)*BR4*BR5</f>
         <v/>
       </c>
       <c r="BS8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BS3)*BS4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BS3)*BS4*BS5</f>
         <v/>
       </c>
       <c r="BT8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BT3)*BT4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BT3)*BT4*BT5</f>
         <v/>
       </c>
       <c r="BU8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BU3)*BU4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BU3)*BU4*BU5</f>
         <v/>
       </c>
       <c r="BV8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BV3)*BV4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BV3)*BV4*BV5</f>
         <v/>
       </c>
       <c r="BW8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BW3)*BW4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BW3)*BW4*BW5</f>
         <v/>
       </c>
       <c r="BX8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BX3)*BX4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BX3)*BX4*BX5</f>
         <v/>
       </c>
       <c r="BY8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BY3)*BY4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BY3)*BY4*BY5</f>
         <v/>
       </c>
       <c r="BZ8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,BZ3)*BZ4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,BZ3)*BZ4*BZ5</f>
         <v/>
       </c>
       <c r="CA8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CA3)*CA4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CA3)*CA4*CA5</f>
         <v/>
       </c>
       <c r="CB8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CB3)*CB4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CB3)*CB4*CB5</f>
         <v/>
       </c>
       <c r="CC8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CC3)*CC4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CC3)*CC4*CC5</f>
         <v/>
       </c>
       <c r="CD8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CD3)*CD4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CD3)*CD4*CD5</f>
         <v/>
       </c>
       <c r="CE8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CE3)*CE4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CE3)*CE4*CE5</f>
         <v/>
       </c>
       <c r="CF8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CF3)*CF4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CF3)*CF4*CF5</f>
         <v/>
       </c>
       <c r="CG8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CG3)*CG4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CG3)*CG4*CG5</f>
         <v/>
       </c>
       <c r="CH8" s="26">
-        <f>INDEX(Premissas!$C$22:$I$22,1,CH3)*CH4</f>
+        <f>INDEX(Premissas!$C$22:$I$22,1,CH3)*CH4*CH5</f>
         <v/>
       </c>
     </row>
@@ -26623,339 +26827,339 @@
         </is>
       </c>
       <c r="C9" s="12">
-        <f>C8/Premissas!$F$70*C5</f>
+        <f>C8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="D9" s="12">
-        <f>D8/Premissas!$F$70*D5</f>
+        <f>D8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>E8/Premissas!$F$70*E5</f>
+        <f>E8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>F8/Premissas!$F$70*F5</f>
+        <f>F8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>G8/Premissas!$F$70*G5</f>
+        <f>G8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>H8/Premissas!$F$70*H5</f>
+        <f>H8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="I9" s="12">
-        <f>I8/Premissas!$F$70*I5</f>
+        <f>I8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="J9" s="12">
-        <f>J8/Premissas!$F$70*J5</f>
+        <f>J8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="K9" s="12">
-        <f>K8/Premissas!$F$70*K5</f>
+        <f>K8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="L9" s="12">
-        <f>L8/Premissas!$F$70*L5</f>
+        <f>L8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="M9" s="12">
-        <f>M8/Premissas!$F$70*M5</f>
+        <f>M8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="N9" s="12">
-        <f>N8/Premissas!$F$70*N5</f>
+        <f>N8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="O9" s="12">
-        <f>O8/Premissas!$F$70*O5</f>
+        <f>O8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="P9" s="12">
-        <f>P8/Premissas!$F$70*P5</f>
+        <f>P8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="Q9" s="12">
-        <f>Q8/Premissas!$F$70*Q5</f>
+        <f>Q8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="R9" s="12">
-        <f>R8/Premissas!$F$70*R5</f>
+        <f>R8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="S9" s="12">
-        <f>S8/Premissas!$F$70*S5</f>
+        <f>S8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="T9" s="12">
-        <f>T8/Premissas!$F$70*T5</f>
+        <f>T8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="U9" s="12">
-        <f>U8/Premissas!$F$70*U5</f>
+        <f>U8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="V9" s="12">
-        <f>V8/Premissas!$F$70*V5</f>
+        <f>V8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="W9" s="12">
-        <f>W8/Premissas!$F$70*W5</f>
+        <f>W8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="X9" s="12">
-        <f>X8/Premissas!$F$70*X5</f>
+        <f>X8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="Y9" s="12">
-        <f>Y8/Premissas!$F$70*Y5</f>
+        <f>Y8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="Z9" s="12">
-        <f>Z8/Premissas!$F$70*Z5</f>
+        <f>Z8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>AA8/Premissas!$F$70*AA5</f>
+        <f>AA8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AB9" s="12">
-        <f>AB8/Premissas!$F$70*AB5</f>
+        <f>AB8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AC9" s="12">
-        <f>AC8/Premissas!$F$70*AC5</f>
+        <f>AC8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AD9" s="12">
-        <f>AD8/Premissas!$F$70*AD5</f>
+        <f>AD8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AE9" s="12">
-        <f>AE8/Premissas!$F$70*AE5</f>
+        <f>AE8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AF9" s="12">
-        <f>AF8/Premissas!$F$70*AF5</f>
+        <f>AF8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>AG8/Premissas!$F$70*AG5</f>
+        <f>AG8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AH9" s="12">
-        <f>AH8/Premissas!$F$70*AH5</f>
+        <f>AH8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AI9" s="12">
-        <f>AI8/Premissas!$F$70*AI5</f>
+        <f>AI8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AJ9" s="12">
-        <f>AJ8/Premissas!$F$70*AJ5</f>
+        <f>AJ8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AK9" s="12">
-        <f>AK8/Premissas!$F$70*AK5</f>
+        <f>AK8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AL9" s="12">
-        <f>AL8/Premissas!$F$70*AL5</f>
+        <f>AL8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AM9" s="12">
-        <f>AM8/Premissas!$F$70*AM5</f>
+        <f>AM8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AN9" s="12">
-        <f>AN8/Premissas!$F$70*AN5</f>
+        <f>AN8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AO9" s="12">
-        <f>AO8/Premissas!$F$70*AO5</f>
+        <f>AO8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AP9" s="12">
-        <f>AP8/Premissas!$F$70*AP5</f>
+        <f>AP8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AQ9" s="12">
-        <f>AQ8/Premissas!$F$70*AQ5</f>
+        <f>AQ8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AR9" s="12">
-        <f>AR8/Premissas!$F$70*AR5</f>
+        <f>AR8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AS9" s="12">
-        <f>AS8/Premissas!$F$70*AS5</f>
+        <f>AS8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AT9" s="12">
-        <f>AT8/Premissas!$F$70*AT5</f>
+        <f>AT8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AU9" s="12">
-        <f>AU8/Premissas!$F$70*AU5</f>
+        <f>AU8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AV9" s="12">
-        <f>AV8/Premissas!$F$70*AV5</f>
+        <f>AV8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AW9" s="12">
-        <f>AW8/Premissas!$F$70*AW5</f>
+        <f>AW8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AX9" s="12">
-        <f>AX8/Premissas!$F$70*AX5</f>
+        <f>AX8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AY9" s="12">
-        <f>AY8/Premissas!$F$70*AY5</f>
+        <f>AY8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="AZ9" s="12">
-        <f>AZ8/Premissas!$F$70*AZ5</f>
+        <f>AZ8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BA9" s="12">
-        <f>BA8/Premissas!$F$70*BA5</f>
+        <f>BA8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BB9" s="12">
-        <f>BB8/Premissas!$F$70*BB5</f>
+        <f>BB8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BC9" s="12">
-        <f>BC8/Premissas!$F$70*BC5</f>
+        <f>BC8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BD9" s="12">
-        <f>BD8/Premissas!$F$70*BD5</f>
+        <f>BD8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BE9" s="12">
-        <f>BE8/Premissas!$F$70*BE5</f>
+        <f>BE8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BF9" s="12">
-        <f>BF8/Premissas!$F$70*BF5</f>
+        <f>BF8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BG9" s="12">
-        <f>BG8/Premissas!$F$70*BG5</f>
+        <f>BG8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BH9" s="12">
-        <f>BH8/Premissas!$F$70*BH5</f>
+        <f>BH8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BI9" s="12">
-        <f>BI8/Premissas!$F$70*BI5</f>
+        <f>BI8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BJ9" s="12">
-        <f>BJ8/Premissas!$F$70*BJ5</f>
+        <f>BJ8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BK9" s="12">
-        <f>BK8/Premissas!$F$70*BK5</f>
+        <f>BK8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BL9" s="12">
-        <f>BL8/Premissas!$F$70*BL5</f>
+        <f>BL8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BM9" s="12">
-        <f>BM8/Premissas!$F$70*BM5</f>
+        <f>BM8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BN9" s="12">
-        <f>BN8/Premissas!$F$70*BN5</f>
+        <f>BN8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BO9" s="12">
-        <f>BO8/Premissas!$F$70*BO5</f>
+        <f>BO8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BP9" s="12">
-        <f>BP8/Premissas!$F$70*BP5</f>
+        <f>BP8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BQ9" s="12">
-        <f>BQ8/Premissas!$F$70*BQ5</f>
+        <f>BQ8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BR9" s="12">
-        <f>BR8/Premissas!$F$70*BR5</f>
+        <f>BR8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BS9" s="12">
-        <f>BS8/Premissas!$F$70*BS5</f>
+        <f>BS8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BT9" s="12">
-        <f>BT8/Premissas!$F$70*BT5</f>
+        <f>BT8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BU9" s="12">
-        <f>BU8/Premissas!$F$70*BU5</f>
+        <f>BU8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BV9" s="12">
-        <f>BV8/Premissas!$F$70*BV5</f>
+        <f>BV8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BW9" s="12">
-        <f>BW8/Premissas!$F$70*BW5</f>
+        <f>BW8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BX9" s="12">
-        <f>BX8/Premissas!$F$70*BX5</f>
+        <f>BX8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BY9" s="12">
-        <f>BY8/Premissas!$F$70*BY5</f>
+        <f>BY8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="BZ9" s="12">
-        <f>BZ8/Premissas!$F$70*BZ5</f>
+        <f>BZ8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="CA9" s="12">
-        <f>CA8/Premissas!$F$70*CA5</f>
+        <f>CA8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="CB9" s="12">
-        <f>CB8/Premissas!$F$70*CB5</f>
+        <f>CB8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="CC9" s="12">
-        <f>CC8/Premissas!$F$70*CC5</f>
+        <f>CC8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="CD9" s="12">
-        <f>CD8/Premissas!$F$70*CD5</f>
+        <f>CD8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="CE9" s="12">
-        <f>CE8/Premissas!$F$70*CE5</f>
+        <f>CE8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="CF9" s="12">
-        <f>CF8/Premissas!$F$70*CF5</f>
+        <f>CF8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="CG9" s="12">
-        <f>CG8/Premissas!$F$70*CG5</f>
+        <f>CG8/Premissas!$F$70</f>
         <v/>
       </c>
       <c r="CH9" s="12">
-        <f>CH8/Premissas!$F$70*CH5</f>
+        <f>CH8/Premissas!$F$70</f>
         <v/>
       </c>
     </row>
@@ -28003,339 +28207,339 @@
         </is>
       </c>
       <c r="C15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(C2&lt;9,Premissas!$F$82+IF(C2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="D15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(D2&lt;9,Premissas!$F$82+IF(D2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="E15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(E2&lt;9,Premissas!$F$82+IF(E2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(F2&lt;9,Premissas!$F$82+IF(F2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="G15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(G2&lt;9,Premissas!$F$82+IF(G2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="H15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(H2&lt;9,Premissas!$F$82+IF(H2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="I15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(I2&lt;9,Premissas!$F$82+IF(I2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="J15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(J2&lt;9,Premissas!$F$82+IF(J2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="K15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(K2&lt;9,Premissas!$F$82+IF(K2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="L15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(L2&lt;9,Premissas!$F$82+IF(L2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="M15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(M2&lt;9,Premissas!$F$82+IF(M2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="N15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(N2&lt;9,Premissas!$F$82+IF(N2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="O15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(O2&lt;9,Premissas!$F$82+IF(O2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="P15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(P2&lt;9,Premissas!$F$82+IF(P2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="Q15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(Q2&lt;9,Premissas!$F$82+IF(Q2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="R15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(R2&lt;9,Premissas!$F$82+IF(R2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="S15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(S2&lt;9,Premissas!$F$82+IF(S2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="T15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(T2&lt;9,Premissas!$F$82+IF(T2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="U15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(U2&lt;9,Premissas!$F$82+IF(U2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="V15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(V2&lt;9,Premissas!$F$82+IF(V2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="W15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(W2&lt;9,Premissas!$F$82+IF(W2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="X15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(X2&lt;9,Premissas!$F$82+IF(X2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="Y15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(Y2&lt;9,Premissas!$F$82+IF(Y2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="Z15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(Z2&lt;9,Premissas!$F$82+IF(Z2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AA15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AA2&lt;9,Premissas!$F$82+IF(AA2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AB15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AB2&lt;9,Premissas!$F$82+IF(AB2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AC15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AC2&lt;9,Premissas!$F$82+IF(AC2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AD15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AD2&lt;9,Premissas!$F$82+IF(AD2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AE15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AE2&lt;9,Premissas!$F$82+IF(AE2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AF15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AF2&lt;9,Premissas!$F$82+IF(AF2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AG15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AG2&lt;9,Premissas!$F$82+IF(AG2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AH15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AH2&lt;9,Premissas!$F$82+IF(AH2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AI15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AI2&lt;9,Premissas!$F$82+IF(AI2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AJ15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AJ2&lt;9,Premissas!$F$82+IF(AJ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AK15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AK2&lt;9,Premissas!$F$82+IF(AK2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AL15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AL2&lt;9,Premissas!$F$82+IF(AL2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AM15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AM2&lt;9,Premissas!$F$82+IF(AM2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AN15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AN2&lt;9,Premissas!$F$82+IF(AN2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AO15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AO2&lt;9,Premissas!$F$82+IF(AO2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AP15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AP2&lt;9,Premissas!$F$82+IF(AP2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AQ15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AQ2&lt;9,Premissas!$F$82+IF(AQ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AR15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AR2&lt;9,Premissas!$F$82+IF(AR2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AS15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AS2&lt;9,Premissas!$F$82+IF(AS2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AT15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AT2&lt;9,Premissas!$F$82+IF(AT2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AU15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AU2&lt;9,Premissas!$F$82+IF(AU2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AV15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AV2&lt;9,Premissas!$F$82+IF(AV2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AW15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AW2&lt;9,Premissas!$F$82+IF(AW2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AX15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AX2&lt;9,Premissas!$F$82+IF(AX2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AY15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AY2&lt;9,Premissas!$F$82+IF(AY2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AZ15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(AZ2&lt;9,Premissas!$F$82+IF(AZ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BA15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BA2&lt;9,Premissas!$F$82+IF(BA2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BB15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BB2&lt;9,Premissas!$F$82+IF(BB2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BC15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BC2&lt;9,Premissas!$F$82+IF(BC2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BD15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BD2&lt;9,Premissas!$F$82+IF(BD2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BE15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BE2&lt;9,Premissas!$F$82+IF(BE2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BF15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BF2&lt;9,Premissas!$F$82+IF(BF2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BG15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BG2&lt;9,Premissas!$F$82+IF(BG2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BH15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BH2&lt;9,Premissas!$F$82+IF(BH2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BI15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BI2&lt;9,Premissas!$F$82+IF(BI2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BJ15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BJ2&lt;9,Premissas!$F$82+IF(BJ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BK15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BK2&lt;9,Premissas!$F$82+IF(BK2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BL15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BL2&lt;9,Premissas!$F$82+IF(BL2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BM15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BM2&lt;9,Premissas!$F$82+IF(BM2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BN15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BN2&lt;9,Premissas!$F$82+IF(BN2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BO15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BO2&lt;9,Premissas!$F$82+IF(BO2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BP15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BP2&lt;9,Premissas!$F$82+IF(BP2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BQ15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BQ2&lt;9,Premissas!$F$82+IF(BQ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BR15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BR2&lt;9,Premissas!$F$82+IF(BR2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BS15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BS2&lt;9,Premissas!$F$82+IF(BS2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BT15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BT2&lt;9,Premissas!$F$82+IF(BT2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BU15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BU2&lt;9,Premissas!$F$82+IF(BU2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BV15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BV2&lt;9,Premissas!$F$82+IF(BV2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BW15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BW2&lt;9,Premissas!$F$82+IF(BW2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BX15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BX2&lt;9,Premissas!$F$82+IF(BX2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BY15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BY2&lt;9,Premissas!$F$82+IF(BY2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BZ15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(BZ2&lt;9,Premissas!$F$82+IF(BZ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CA15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(CA2&lt;9,Premissas!$F$82+IF(CA2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CB15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(CB2&lt;9,Premissas!$F$82+IF(CB2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CC15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(CC2&lt;9,Premissas!$F$82+IF(CC2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CD15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(CD2&lt;9,Premissas!$F$82+IF(CD2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CE15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(CE2&lt;9,Premissas!$F$82+IF(CE2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CF15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(CF2&lt;9,Premissas!$F$82+IF(CF2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CG15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(CG2&lt;9,Premissas!$F$82+IF(CG2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CH15" s="27">
-        <f>Premissas!$F$76</f>
+        <f>Premissas!$F$76+IF(CH2&lt;9,Premissas!$F$82+IF(CH2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
     </row>
@@ -29383,339 +29587,339 @@
         </is>
       </c>
       <c r="C21" s="27">
-        <f>Premissas!$F$82+IF(C2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(C2&gt;=9,Premissas!$F$82+IF(C2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="D21" s="27">
-        <f>Premissas!$F$82+IF(D2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(D2&gt;=9,Premissas!$F$82+IF(D2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="E21" s="27">
-        <f>Premissas!$F$82+IF(E2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(E2&gt;=9,Premissas!$F$82+IF(E2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="F21" s="27">
-        <f>Premissas!$F$82+IF(F2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(F2&gt;=9,Premissas!$F$82+IF(F2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="G21" s="27">
-        <f>Premissas!$F$82+IF(G2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(G2&gt;=9,Premissas!$F$82+IF(G2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="H21" s="27">
-        <f>Premissas!$F$82+IF(H2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(H2&gt;=9,Premissas!$F$82+IF(H2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="I21" s="27">
-        <f>Premissas!$F$82+IF(I2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(I2&gt;=9,Premissas!$F$82+IF(I2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="J21" s="27">
-        <f>Premissas!$F$82+IF(J2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(J2&gt;=9,Premissas!$F$82+IF(J2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="K21" s="27">
-        <f>Premissas!$F$82+IF(K2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(K2&gt;=9,Premissas!$F$82+IF(K2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="L21" s="27">
-        <f>Premissas!$F$82+IF(L2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(L2&gt;=9,Premissas!$F$82+IF(L2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="M21" s="27">
-        <f>Premissas!$F$82+IF(M2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(M2&gt;=9,Premissas!$F$82+IF(M2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="N21" s="27">
-        <f>Premissas!$F$82+IF(N2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(N2&gt;=9,Premissas!$F$82+IF(N2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="O21" s="27">
-        <f>Premissas!$F$82+IF(O2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(O2&gt;=9,Premissas!$F$82+IF(O2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="P21" s="27">
-        <f>Premissas!$F$82+IF(P2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(P2&gt;=9,Premissas!$F$82+IF(P2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="Q21" s="27">
-        <f>Premissas!$F$82+IF(Q2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(Q2&gt;=9,Premissas!$F$82+IF(Q2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="R21" s="27">
-        <f>Premissas!$F$82+IF(R2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(R2&gt;=9,Premissas!$F$82+IF(R2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="S21" s="27">
-        <f>Premissas!$F$82+IF(S2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(S2&gt;=9,Premissas!$F$82+IF(S2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="T21" s="27">
-        <f>Premissas!$F$82+IF(T2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(T2&gt;=9,Premissas!$F$82+IF(T2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="U21" s="27">
-        <f>Premissas!$F$82+IF(U2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(U2&gt;=9,Premissas!$F$82+IF(U2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="V21" s="27">
-        <f>Premissas!$F$82+IF(V2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(V2&gt;=9,Premissas!$F$82+IF(V2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="W21" s="27">
-        <f>Premissas!$F$82+IF(W2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(W2&gt;=9,Premissas!$F$82+IF(W2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="X21" s="27">
-        <f>Premissas!$F$82+IF(X2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(X2&gt;=9,Premissas!$F$82+IF(X2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="Y21" s="27">
-        <f>Premissas!$F$82+IF(Y2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(Y2&gt;=9,Premissas!$F$82+IF(Y2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="Z21" s="27">
-        <f>Premissas!$F$82+IF(Z2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(Z2&gt;=9,Premissas!$F$82+IF(Z2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AA21" s="27">
-        <f>Premissas!$F$82+IF(AA2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AA2&gt;=9,Premissas!$F$82+IF(AA2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AB21" s="27">
-        <f>Premissas!$F$82+IF(AB2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AB2&gt;=9,Premissas!$F$82+IF(AB2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AC21" s="27">
-        <f>Premissas!$F$82+IF(AC2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AC2&gt;=9,Premissas!$F$82+IF(AC2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AD21" s="27">
-        <f>Premissas!$F$82+IF(AD2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AD2&gt;=9,Premissas!$F$82+IF(AD2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AE21" s="27">
-        <f>Premissas!$F$82+IF(AE2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AE2&gt;=9,Premissas!$F$82+IF(AE2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AF21" s="27">
-        <f>Premissas!$F$82+IF(AF2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AF2&gt;=9,Premissas!$F$82+IF(AF2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AG21" s="27">
-        <f>Premissas!$F$82+IF(AG2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AG2&gt;=9,Premissas!$F$82+IF(AG2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AH21" s="27">
-        <f>Premissas!$F$82+IF(AH2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AH2&gt;=9,Premissas!$F$82+IF(AH2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AI21" s="27">
-        <f>Premissas!$F$82+IF(AI2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AI2&gt;=9,Premissas!$F$82+IF(AI2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AJ21" s="27">
-        <f>Premissas!$F$82+IF(AJ2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AJ2&gt;=9,Premissas!$F$82+IF(AJ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AK21" s="27">
-        <f>Premissas!$F$82+IF(AK2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AK2&gt;=9,Premissas!$F$82+IF(AK2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AL21" s="27">
-        <f>Premissas!$F$82+IF(AL2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AL2&gt;=9,Premissas!$F$82+IF(AL2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AM21" s="27">
-        <f>Premissas!$F$82+IF(AM2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AM2&gt;=9,Premissas!$F$82+IF(AM2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AN21" s="27">
-        <f>Premissas!$F$82+IF(AN2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AN2&gt;=9,Premissas!$F$82+IF(AN2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AO21" s="27">
-        <f>Premissas!$F$82+IF(AO2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AO2&gt;=9,Premissas!$F$82+IF(AO2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AP21" s="27">
-        <f>Premissas!$F$82+IF(AP2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AP2&gt;=9,Premissas!$F$82+IF(AP2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AQ21" s="27">
-        <f>Premissas!$F$82+IF(AQ2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AQ2&gt;=9,Premissas!$F$82+IF(AQ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AR21" s="27">
-        <f>Premissas!$F$82+IF(AR2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AR2&gt;=9,Premissas!$F$82+IF(AR2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AS21" s="27">
-        <f>Premissas!$F$82+IF(AS2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AS2&gt;=9,Premissas!$F$82+IF(AS2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AT21" s="27">
-        <f>Premissas!$F$82+IF(AT2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AT2&gt;=9,Premissas!$F$82+IF(AT2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AU21" s="27">
-        <f>Premissas!$F$82+IF(AU2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AU2&gt;=9,Premissas!$F$82+IF(AU2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AV21" s="27">
-        <f>Premissas!$F$82+IF(AV2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AV2&gt;=9,Premissas!$F$82+IF(AV2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AW21" s="27">
-        <f>Premissas!$F$82+IF(AW2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AW2&gt;=9,Premissas!$F$82+IF(AW2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AX21" s="27">
-        <f>Premissas!$F$82+IF(AX2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AX2&gt;=9,Premissas!$F$82+IF(AX2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AY21" s="27">
-        <f>Premissas!$F$82+IF(AY2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AY2&gt;=9,Premissas!$F$82+IF(AY2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="AZ21" s="27">
-        <f>Premissas!$F$82+IF(AZ2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(AZ2&gt;=9,Premissas!$F$82+IF(AZ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BA21" s="27">
-        <f>Premissas!$F$82+IF(BA2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BA2&gt;=9,Premissas!$F$82+IF(BA2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BB21" s="27">
-        <f>Premissas!$F$82+IF(BB2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BB2&gt;=9,Premissas!$F$82+IF(BB2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BC21" s="27">
-        <f>Premissas!$F$82+IF(BC2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BC2&gt;=9,Premissas!$F$82+IF(BC2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BD21" s="27">
-        <f>Premissas!$F$82+IF(BD2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BD2&gt;=9,Premissas!$F$82+IF(BD2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BE21" s="27">
-        <f>Premissas!$F$82+IF(BE2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BE2&gt;=9,Premissas!$F$82+IF(BE2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BF21" s="27">
-        <f>Premissas!$F$82+IF(BF2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BF2&gt;=9,Premissas!$F$82+IF(BF2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BG21" s="27">
-        <f>Premissas!$F$82+IF(BG2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BG2&gt;=9,Premissas!$F$82+IF(BG2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BH21" s="27">
-        <f>Premissas!$F$82+IF(BH2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BH2&gt;=9,Premissas!$F$82+IF(BH2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BI21" s="27">
-        <f>Premissas!$F$82+IF(BI2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BI2&gt;=9,Premissas!$F$82+IF(BI2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BJ21" s="27">
-        <f>Premissas!$F$82+IF(BJ2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BJ2&gt;=9,Premissas!$F$82+IF(BJ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BK21" s="27">
-        <f>Premissas!$F$82+IF(BK2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BK2&gt;=9,Premissas!$F$82+IF(BK2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BL21" s="27">
-        <f>Premissas!$F$82+IF(BL2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BL2&gt;=9,Premissas!$F$82+IF(BL2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BM21" s="27">
-        <f>Premissas!$F$82+IF(BM2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BM2&gt;=9,Premissas!$F$82+IF(BM2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BN21" s="27">
-        <f>Premissas!$F$82+IF(BN2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BN2&gt;=9,Premissas!$F$82+IF(BN2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BO21" s="27">
-        <f>Premissas!$F$82+IF(BO2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BO2&gt;=9,Premissas!$F$82+IF(BO2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BP21" s="27">
-        <f>Premissas!$F$82+IF(BP2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BP2&gt;=9,Premissas!$F$82+IF(BP2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BQ21" s="27">
-        <f>Premissas!$F$82+IF(BQ2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BQ2&gt;=9,Premissas!$F$82+IF(BQ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BR21" s="27">
-        <f>Premissas!$F$82+IF(BR2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BR2&gt;=9,Premissas!$F$82+IF(BR2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BS21" s="27">
-        <f>Premissas!$F$82+IF(BS2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BS2&gt;=9,Premissas!$F$82+IF(BS2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BT21" s="27">
-        <f>Premissas!$F$82+IF(BT2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BT2&gt;=9,Premissas!$F$82+IF(BT2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BU21" s="27">
-        <f>Premissas!$F$82+IF(BU2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BU2&gt;=9,Premissas!$F$82+IF(BU2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BV21" s="27">
-        <f>Premissas!$F$82+IF(BV2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BV2&gt;=9,Premissas!$F$82+IF(BV2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BW21" s="27">
-        <f>Premissas!$F$82+IF(BW2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BW2&gt;=9,Premissas!$F$82+IF(BW2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BX21" s="27">
-        <f>Premissas!$F$82+IF(BX2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BX2&gt;=9,Premissas!$F$82+IF(BX2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BY21" s="27">
-        <f>Premissas!$F$82+IF(BY2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BY2&gt;=9,Premissas!$F$82+IF(BY2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="BZ21" s="27">
-        <f>Premissas!$F$82+IF(BZ2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(BZ2&gt;=9,Premissas!$F$82+IF(BZ2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CA21" s="27">
-        <f>Premissas!$F$82+IF(CA2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(CA2&gt;=9,Premissas!$F$82+IF(CA2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CB21" s="27">
-        <f>Premissas!$F$82+IF(CB2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(CB2&gt;=9,Premissas!$F$82+IF(CB2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CC21" s="27">
-        <f>Premissas!$F$82+IF(CC2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(CC2&gt;=9,Premissas!$F$82+IF(CC2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CD21" s="27">
-        <f>Premissas!$F$82+IF(CD2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(CD2&gt;=9,Premissas!$F$82+IF(CD2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CE21" s="27">
-        <f>Premissas!$F$82+IF(CE2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(CE2&gt;=9,Premissas!$F$82+IF(CE2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CF21" s="27">
-        <f>Premissas!$F$82+IF(CF2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(CF2&gt;=9,Premissas!$F$82+IF(CF2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CG21" s="27">
-        <f>Premissas!$F$82+IF(CG2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(CG2&gt;=9,Premissas!$F$82+IF(CG2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
       <c r="CH21" s="27">
-        <f>Premissas!$F$82+IF(CH2&lt;13,Premissas!$F$89,0)</f>
+        <f>IF(CH2&gt;=9,Premissas!$F$82+IF(CH2&lt;13,Premissas!$F$89,0),0)</f>
         <v/>
       </c>
     </row>
@@ -36263,343 +36467,343 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Custo direto (IA, ferramentas, hospedagem)</t>
+          <t>Custo direto (IA, ferramentas, hospedagem, implantação)</t>
         </is>
       </c>
       <c r="C47" s="26">
-        <f>C18*Premissas!$F$78+C24*Premissas!$F$84+C30*Premissas!$F$91</f>
+        <f>C18*Premissas!$F$78+C24*Premissas!$F$84+C30*Premissas!$F$91+C12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="D47" s="26">
-        <f>D18*Premissas!$F$78+D24*Premissas!$F$84+D30*Premissas!$F$91</f>
+        <f>D18*Premissas!$F$78+D24*Premissas!$F$84+D30*Premissas!$F$91+D12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="E47" s="26">
-        <f>E18*Premissas!$F$78+E24*Premissas!$F$84+E30*Premissas!$F$91</f>
+        <f>E18*Premissas!$F$78+E24*Premissas!$F$84+E30*Premissas!$F$91+E12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="F47" s="26">
-        <f>F18*Premissas!$F$78+F24*Premissas!$F$84+F30*Premissas!$F$91</f>
+        <f>F18*Premissas!$F$78+F24*Premissas!$F$84+F30*Premissas!$F$91+F12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="G47" s="26">
-        <f>G18*Premissas!$F$78+G24*Premissas!$F$84+G30*Premissas!$F$91</f>
+        <f>G18*Premissas!$F$78+G24*Premissas!$F$84+G30*Premissas!$F$91+G12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="H47" s="26">
-        <f>H18*Premissas!$F$78+H24*Premissas!$F$84+H30*Premissas!$F$91</f>
+        <f>H18*Premissas!$F$78+H24*Premissas!$F$84+H30*Premissas!$F$91+H12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="I47" s="26">
-        <f>I18*Premissas!$F$78+I24*Premissas!$F$84+I30*Premissas!$F$91</f>
+        <f>I18*Premissas!$F$78+I24*Premissas!$F$84+I30*Premissas!$F$91+I12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="J47" s="26">
-        <f>J18*Premissas!$F$78+J24*Premissas!$F$84+J30*Premissas!$F$91</f>
+        <f>J18*Premissas!$F$78+J24*Premissas!$F$84+J30*Premissas!$F$91+J12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="K47" s="26">
-        <f>K18*Premissas!$F$78+K24*Premissas!$F$84+K30*Premissas!$F$91</f>
+        <f>K18*Premissas!$F$78+K24*Premissas!$F$84+K30*Premissas!$F$91+K12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="L47" s="26">
-        <f>L18*Premissas!$F$78+L24*Premissas!$F$84+L30*Premissas!$F$91</f>
+        <f>L18*Premissas!$F$78+L24*Premissas!$F$84+L30*Premissas!$F$91+L12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="M47" s="26">
-        <f>M18*Premissas!$F$78+M24*Premissas!$F$84+M30*Premissas!$F$91</f>
+        <f>M18*Premissas!$F$78+M24*Premissas!$F$84+M30*Premissas!$F$91+M12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="N47" s="26">
-        <f>N18*Premissas!$F$78+N24*Premissas!$F$84+N30*Premissas!$F$91</f>
+        <f>N18*Premissas!$F$78+N24*Premissas!$F$84+N30*Premissas!$F$91+N12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="O47" s="26">
-        <f>O18*Premissas!$F$78+O24*Premissas!$F$84+O30*Premissas!$F$91</f>
+        <f>O18*Premissas!$F$78+O24*Premissas!$F$84+O30*Premissas!$F$91+O12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="P47" s="26">
-        <f>P18*Premissas!$F$78+P24*Premissas!$F$84+P30*Premissas!$F$91</f>
+        <f>P18*Premissas!$F$78+P24*Premissas!$F$84+P30*Premissas!$F$91+P12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="Q47" s="26">
-        <f>Q18*Premissas!$F$78+Q24*Premissas!$F$84+Q30*Premissas!$F$91</f>
+        <f>Q18*Premissas!$F$78+Q24*Premissas!$F$84+Q30*Premissas!$F$91+Q12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="R47" s="26">
-        <f>R18*Premissas!$F$78+R24*Premissas!$F$84+R30*Premissas!$F$91</f>
+        <f>R18*Premissas!$F$78+R24*Premissas!$F$84+R30*Premissas!$F$91+R12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="S47" s="26">
-        <f>S18*Premissas!$F$78+S24*Premissas!$F$84+S30*Premissas!$F$91</f>
+        <f>S18*Premissas!$F$78+S24*Premissas!$F$84+S30*Premissas!$F$91+S12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="T47" s="26">
-        <f>T18*Premissas!$F$78+T24*Premissas!$F$84+T30*Premissas!$F$91</f>
+        <f>T18*Premissas!$F$78+T24*Premissas!$F$84+T30*Premissas!$F$91+T12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="U47" s="26">
-        <f>U18*Premissas!$F$78+U24*Premissas!$F$84+U30*Premissas!$F$91</f>
+        <f>U18*Premissas!$F$78+U24*Premissas!$F$84+U30*Premissas!$F$91+U12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="V47" s="26">
-        <f>V18*Premissas!$F$78+V24*Premissas!$F$84+V30*Premissas!$F$91</f>
+        <f>V18*Premissas!$F$78+V24*Premissas!$F$84+V30*Premissas!$F$91+V12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="W47" s="26">
-        <f>W18*Premissas!$F$78+W24*Premissas!$F$84+W30*Premissas!$F$91</f>
+        <f>W18*Premissas!$F$78+W24*Premissas!$F$84+W30*Premissas!$F$91+W12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="X47" s="26">
-        <f>X18*Premissas!$F$78+X24*Premissas!$F$84+X30*Premissas!$F$91</f>
+        <f>X18*Premissas!$F$78+X24*Premissas!$F$84+X30*Premissas!$F$91+X12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="Y47" s="26">
-        <f>Y18*Premissas!$F$78+Y24*Premissas!$F$84+Y30*Premissas!$F$91</f>
+        <f>Y18*Premissas!$F$78+Y24*Premissas!$F$84+Y30*Premissas!$F$91+Y12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="Z47" s="26">
-        <f>Z18*Premissas!$F$78+Z24*Premissas!$F$84+Z30*Premissas!$F$91</f>
+        <f>Z18*Premissas!$F$78+Z24*Premissas!$F$84+Z30*Premissas!$F$91+Z12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AA47" s="26">
-        <f>AA18*Premissas!$F$78+AA24*Premissas!$F$84+AA30*Premissas!$F$91</f>
+        <f>AA18*Premissas!$F$78+AA24*Premissas!$F$84+AA30*Premissas!$F$91+AA12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AB47" s="26">
-        <f>AB18*Premissas!$F$78+AB24*Premissas!$F$84+AB30*Premissas!$F$91</f>
+        <f>AB18*Premissas!$F$78+AB24*Premissas!$F$84+AB30*Premissas!$F$91+AB12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AC47" s="26">
-        <f>AC18*Premissas!$F$78+AC24*Premissas!$F$84+AC30*Premissas!$F$91</f>
+        <f>AC18*Premissas!$F$78+AC24*Premissas!$F$84+AC30*Premissas!$F$91+AC12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AD47" s="26">
-        <f>AD18*Premissas!$F$78+AD24*Premissas!$F$84+AD30*Premissas!$F$91</f>
+        <f>AD18*Premissas!$F$78+AD24*Premissas!$F$84+AD30*Premissas!$F$91+AD12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AE47" s="26">
-        <f>AE18*Premissas!$F$78+AE24*Premissas!$F$84+AE30*Premissas!$F$91</f>
+        <f>AE18*Premissas!$F$78+AE24*Premissas!$F$84+AE30*Premissas!$F$91+AE12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AF47" s="26">
-        <f>AF18*Premissas!$F$78+AF24*Premissas!$F$84+AF30*Premissas!$F$91</f>
+        <f>AF18*Premissas!$F$78+AF24*Premissas!$F$84+AF30*Premissas!$F$91+AF12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AG47" s="26">
-        <f>AG18*Premissas!$F$78+AG24*Premissas!$F$84+AG30*Premissas!$F$91</f>
+        <f>AG18*Premissas!$F$78+AG24*Premissas!$F$84+AG30*Premissas!$F$91+AG12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AH47" s="26">
-        <f>AH18*Premissas!$F$78+AH24*Premissas!$F$84+AH30*Premissas!$F$91</f>
+        <f>AH18*Premissas!$F$78+AH24*Premissas!$F$84+AH30*Premissas!$F$91+AH12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AI47" s="26">
-        <f>AI18*Premissas!$F$78+AI24*Premissas!$F$84+AI30*Premissas!$F$91</f>
+        <f>AI18*Premissas!$F$78+AI24*Premissas!$F$84+AI30*Premissas!$F$91+AI12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AJ47" s="26">
-        <f>AJ18*Premissas!$F$78+AJ24*Premissas!$F$84+AJ30*Premissas!$F$91</f>
+        <f>AJ18*Premissas!$F$78+AJ24*Premissas!$F$84+AJ30*Premissas!$F$91+AJ12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AK47" s="26">
-        <f>AK18*Premissas!$F$78+AK24*Premissas!$F$84+AK30*Premissas!$F$91</f>
+        <f>AK18*Premissas!$F$78+AK24*Premissas!$F$84+AK30*Premissas!$F$91+AK12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AL47" s="26">
-        <f>AL18*Premissas!$F$78+AL24*Premissas!$F$84+AL30*Premissas!$F$91</f>
+        <f>AL18*Premissas!$F$78+AL24*Premissas!$F$84+AL30*Premissas!$F$91+AL12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AM47" s="26">
-        <f>AM18*Premissas!$F$78+AM24*Premissas!$F$84+AM30*Premissas!$F$91</f>
+        <f>AM18*Premissas!$F$78+AM24*Premissas!$F$84+AM30*Premissas!$F$91+AM12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AN47" s="26">
-        <f>AN18*Premissas!$F$78+AN24*Premissas!$F$84+AN30*Premissas!$F$91</f>
+        <f>AN18*Premissas!$F$78+AN24*Premissas!$F$84+AN30*Premissas!$F$91+AN12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AO47" s="26">
-        <f>AO18*Premissas!$F$78+AO24*Premissas!$F$84+AO30*Premissas!$F$91</f>
+        <f>AO18*Premissas!$F$78+AO24*Premissas!$F$84+AO30*Premissas!$F$91+AO12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AP47" s="26">
-        <f>AP18*Premissas!$F$78+AP24*Premissas!$F$84+AP30*Premissas!$F$91</f>
+        <f>AP18*Premissas!$F$78+AP24*Premissas!$F$84+AP30*Premissas!$F$91+AP12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AQ47" s="26">
-        <f>AQ18*Premissas!$F$78+AQ24*Premissas!$F$84+AQ30*Premissas!$F$91</f>
+        <f>AQ18*Premissas!$F$78+AQ24*Premissas!$F$84+AQ30*Premissas!$F$91+AQ12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AR47" s="26">
-        <f>AR18*Premissas!$F$78+AR24*Premissas!$F$84+AR30*Premissas!$F$91</f>
+        <f>AR18*Premissas!$F$78+AR24*Premissas!$F$84+AR30*Premissas!$F$91+AR12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AS47" s="26">
-        <f>AS18*Premissas!$F$78+AS24*Premissas!$F$84+AS30*Premissas!$F$91</f>
+        <f>AS18*Premissas!$F$78+AS24*Premissas!$F$84+AS30*Premissas!$F$91+AS12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AT47" s="26">
-        <f>AT18*Premissas!$F$78+AT24*Premissas!$F$84+AT30*Premissas!$F$91</f>
+        <f>AT18*Premissas!$F$78+AT24*Premissas!$F$84+AT30*Premissas!$F$91+AT12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AU47" s="26">
-        <f>AU18*Premissas!$F$78+AU24*Premissas!$F$84+AU30*Premissas!$F$91</f>
+        <f>AU18*Premissas!$F$78+AU24*Premissas!$F$84+AU30*Premissas!$F$91+AU12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AV47" s="26">
-        <f>AV18*Premissas!$F$78+AV24*Premissas!$F$84+AV30*Premissas!$F$91</f>
+        <f>AV18*Premissas!$F$78+AV24*Premissas!$F$84+AV30*Premissas!$F$91+AV12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AW47" s="26">
-        <f>AW18*Premissas!$F$78+AW24*Premissas!$F$84+AW30*Premissas!$F$91</f>
+        <f>AW18*Premissas!$F$78+AW24*Premissas!$F$84+AW30*Premissas!$F$91+AW12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AX47" s="26">
-        <f>AX18*Premissas!$F$78+AX24*Premissas!$F$84+AX30*Premissas!$F$91</f>
+        <f>AX18*Premissas!$F$78+AX24*Premissas!$F$84+AX30*Premissas!$F$91+AX12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AY47" s="26">
-        <f>AY18*Premissas!$F$78+AY24*Premissas!$F$84+AY30*Premissas!$F$91</f>
+        <f>AY18*Premissas!$F$78+AY24*Premissas!$F$84+AY30*Premissas!$F$91+AY12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="AZ47" s="26">
-        <f>AZ18*Premissas!$F$78+AZ24*Premissas!$F$84+AZ30*Premissas!$F$91</f>
+        <f>AZ18*Premissas!$F$78+AZ24*Premissas!$F$84+AZ30*Premissas!$F$91+AZ12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BA47" s="26">
-        <f>BA18*Premissas!$F$78+BA24*Premissas!$F$84+BA30*Premissas!$F$91</f>
+        <f>BA18*Premissas!$F$78+BA24*Premissas!$F$84+BA30*Premissas!$F$91+BA12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BB47" s="26">
-        <f>BB18*Premissas!$F$78+BB24*Premissas!$F$84+BB30*Premissas!$F$91</f>
+        <f>BB18*Premissas!$F$78+BB24*Premissas!$F$84+BB30*Premissas!$F$91+BB12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BC47" s="26">
-        <f>BC18*Premissas!$F$78+BC24*Premissas!$F$84+BC30*Premissas!$F$91</f>
+        <f>BC18*Premissas!$F$78+BC24*Premissas!$F$84+BC30*Premissas!$F$91+BC12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BD47" s="26">
-        <f>BD18*Premissas!$F$78+BD24*Premissas!$F$84+BD30*Premissas!$F$91</f>
+        <f>BD18*Premissas!$F$78+BD24*Premissas!$F$84+BD30*Premissas!$F$91+BD12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BE47" s="26">
-        <f>BE18*Premissas!$F$78+BE24*Premissas!$F$84+BE30*Premissas!$F$91</f>
+        <f>BE18*Premissas!$F$78+BE24*Premissas!$F$84+BE30*Premissas!$F$91+BE12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BF47" s="26">
-        <f>BF18*Premissas!$F$78+BF24*Premissas!$F$84+BF30*Premissas!$F$91</f>
+        <f>BF18*Premissas!$F$78+BF24*Premissas!$F$84+BF30*Premissas!$F$91+BF12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BG47" s="26">
-        <f>BG18*Premissas!$F$78+BG24*Premissas!$F$84+BG30*Premissas!$F$91</f>
+        <f>BG18*Premissas!$F$78+BG24*Premissas!$F$84+BG30*Premissas!$F$91+BG12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BH47" s="26">
-        <f>BH18*Premissas!$F$78+BH24*Premissas!$F$84+BH30*Premissas!$F$91</f>
+        <f>BH18*Premissas!$F$78+BH24*Premissas!$F$84+BH30*Premissas!$F$91+BH12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BI47" s="26">
-        <f>BI18*Premissas!$F$78+BI24*Premissas!$F$84+BI30*Premissas!$F$91</f>
+        <f>BI18*Premissas!$F$78+BI24*Premissas!$F$84+BI30*Premissas!$F$91+BI12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BJ47" s="26">
-        <f>BJ18*Premissas!$F$78+BJ24*Premissas!$F$84+BJ30*Premissas!$F$91</f>
+        <f>BJ18*Premissas!$F$78+BJ24*Premissas!$F$84+BJ30*Premissas!$F$91+BJ12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BK47" s="26">
-        <f>BK18*Premissas!$F$78+BK24*Premissas!$F$84+BK30*Premissas!$F$91</f>
+        <f>BK18*Premissas!$F$78+BK24*Premissas!$F$84+BK30*Premissas!$F$91+BK12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BL47" s="26">
-        <f>BL18*Premissas!$F$78+BL24*Premissas!$F$84+BL30*Premissas!$F$91</f>
+        <f>BL18*Premissas!$F$78+BL24*Premissas!$F$84+BL30*Premissas!$F$91+BL12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BM47" s="26">
-        <f>BM18*Premissas!$F$78+BM24*Premissas!$F$84+BM30*Premissas!$F$91</f>
+        <f>BM18*Premissas!$F$78+BM24*Premissas!$F$84+BM30*Premissas!$F$91+BM12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BN47" s="26">
-        <f>BN18*Premissas!$F$78+BN24*Premissas!$F$84+BN30*Premissas!$F$91</f>
+        <f>BN18*Premissas!$F$78+BN24*Premissas!$F$84+BN30*Premissas!$F$91+BN12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BO47" s="26">
-        <f>BO18*Premissas!$F$78+BO24*Premissas!$F$84+BO30*Premissas!$F$91</f>
+        <f>BO18*Premissas!$F$78+BO24*Premissas!$F$84+BO30*Premissas!$F$91+BO12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BP47" s="26">
-        <f>BP18*Premissas!$F$78+BP24*Premissas!$F$84+BP30*Premissas!$F$91</f>
+        <f>BP18*Premissas!$F$78+BP24*Premissas!$F$84+BP30*Premissas!$F$91+BP12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BQ47" s="26">
-        <f>BQ18*Premissas!$F$78+BQ24*Premissas!$F$84+BQ30*Premissas!$F$91</f>
+        <f>BQ18*Premissas!$F$78+BQ24*Premissas!$F$84+BQ30*Premissas!$F$91+BQ12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BR47" s="26">
-        <f>BR18*Premissas!$F$78+BR24*Premissas!$F$84+BR30*Premissas!$F$91</f>
+        <f>BR18*Premissas!$F$78+BR24*Premissas!$F$84+BR30*Premissas!$F$91+BR12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BS47" s="26">
-        <f>BS18*Premissas!$F$78+BS24*Premissas!$F$84+BS30*Premissas!$F$91</f>
+        <f>BS18*Premissas!$F$78+BS24*Premissas!$F$84+BS30*Premissas!$F$91+BS12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BT47" s="26">
-        <f>BT18*Premissas!$F$78+BT24*Premissas!$F$84+BT30*Premissas!$F$91</f>
+        <f>BT18*Premissas!$F$78+BT24*Premissas!$F$84+BT30*Premissas!$F$91+BT12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BU47" s="26">
-        <f>BU18*Premissas!$F$78+BU24*Premissas!$F$84+BU30*Premissas!$F$91</f>
+        <f>BU18*Premissas!$F$78+BU24*Premissas!$F$84+BU30*Premissas!$F$91+BU12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BV47" s="26">
-        <f>BV18*Premissas!$F$78+BV24*Premissas!$F$84+BV30*Premissas!$F$91</f>
+        <f>BV18*Premissas!$F$78+BV24*Premissas!$F$84+BV30*Premissas!$F$91+BV12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BW47" s="26">
-        <f>BW18*Premissas!$F$78+BW24*Premissas!$F$84+BW30*Premissas!$F$91</f>
+        <f>BW18*Premissas!$F$78+BW24*Premissas!$F$84+BW30*Premissas!$F$91+BW12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BX47" s="26">
-        <f>BX18*Premissas!$F$78+BX24*Premissas!$F$84+BX30*Premissas!$F$91</f>
+        <f>BX18*Premissas!$F$78+BX24*Premissas!$F$84+BX30*Premissas!$F$91+BX12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BY47" s="26">
-        <f>BY18*Premissas!$F$78+BY24*Premissas!$F$84+BY30*Premissas!$F$91</f>
+        <f>BY18*Premissas!$F$78+BY24*Premissas!$F$84+BY30*Premissas!$F$91+BY12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="BZ47" s="26">
-        <f>BZ18*Premissas!$F$78+BZ24*Premissas!$F$84+BZ30*Premissas!$F$91</f>
+        <f>BZ18*Premissas!$F$78+BZ24*Premissas!$F$84+BZ30*Premissas!$F$91+BZ12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="CA47" s="26">
-        <f>CA18*Premissas!$F$78+CA24*Premissas!$F$84+CA30*Premissas!$F$91</f>
+        <f>CA18*Premissas!$F$78+CA24*Premissas!$F$84+CA30*Premissas!$F$91+CA12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="CB47" s="26">
-        <f>CB18*Premissas!$F$78+CB24*Premissas!$F$84+CB30*Premissas!$F$91</f>
+        <f>CB18*Premissas!$F$78+CB24*Premissas!$F$84+CB30*Premissas!$F$91+CB12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="CC47" s="26">
-        <f>CC18*Premissas!$F$78+CC24*Premissas!$F$84+CC30*Premissas!$F$91</f>
+        <f>CC18*Premissas!$F$78+CC24*Premissas!$F$84+CC30*Premissas!$F$91+CC12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="CD47" s="26">
-        <f>CD18*Premissas!$F$78+CD24*Premissas!$F$84+CD30*Premissas!$F$91</f>
+        <f>CD18*Premissas!$F$78+CD24*Premissas!$F$84+CD30*Premissas!$F$91+CD12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="CE47" s="26">
-        <f>CE18*Premissas!$F$78+CE24*Premissas!$F$84+CE30*Premissas!$F$91</f>
+        <f>CE18*Premissas!$F$78+CE24*Premissas!$F$84+CE30*Premissas!$F$91+CE12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="CF47" s="26">
-        <f>CF18*Premissas!$F$78+CF24*Premissas!$F$84+CF30*Premissas!$F$91</f>
+        <f>CF18*Premissas!$F$78+CF24*Premissas!$F$84+CF30*Premissas!$F$91+CF12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="CG47" s="26">
-        <f>CG18*Premissas!$F$78+CG24*Premissas!$F$84+CG30*Premissas!$F$91</f>
+        <f>CG18*Premissas!$F$78+CG24*Premissas!$F$84+CG30*Premissas!$F$91+CG12*Premissas!$F$106</f>
         <v/>
       </c>
       <c r="CH47" s="26">
-        <f>CH18*Premissas!$F$78+CH24*Premissas!$F$84+CH30*Premissas!$F$91</f>
+        <f>CH18*Premissas!$F$78+CH24*Premissas!$F$84+CH30*Premissas!$F$91+CH12*Premissas!$F$106</f>
         <v/>
       </c>
     </row>
@@ -40044,343 +40248,343 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Comissões de parceria</t>
+          <t>Comissões de parceria e meses grátis de indicação</t>
         </is>
       </c>
       <c r="C60" s="26">
-        <f>C10*Premissas!$F$71</f>
+        <f>C10*Premissas!$F$71+C11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="D60" s="26">
-        <f>D10*Premissas!$F$71</f>
+        <f>D10*Premissas!$F$71+D11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="E60" s="26">
-        <f>E10*Premissas!$F$71</f>
+        <f>E10*Premissas!$F$71+E11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="F60" s="26">
-        <f>F10*Premissas!$F$71</f>
+        <f>F10*Premissas!$F$71+F11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="G60" s="26">
-        <f>G10*Premissas!$F$71</f>
+        <f>G10*Premissas!$F$71+G11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="H60" s="26">
-        <f>H10*Premissas!$F$71</f>
+        <f>H10*Premissas!$F$71+H11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="I60" s="26">
-        <f>I10*Premissas!$F$71</f>
+        <f>I10*Premissas!$F$71+I11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="J60" s="26">
-        <f>J10*Premissas!$F$71</f>
+        <f>J10*Premissas!$F$71+J11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="K60" s="26">
-        <f>K10*Premissas!$F$71</f>
+        <f>K10*Premissas!$F$71+K11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="L60" s="26">
-        <f>L10*Premissas!$F$71</f>
+        <f>L10*Premissas!$F$71+L11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="M60" s="26">
-        <f>M10*Premissas!$F$71</f>
+        <f>M10*Premissas!$F$71+M11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="N60" s="26">
-        <f>N10*Premissas!$F$71</f>
+        <f>N10*Premissas!$F$71+N11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="O60" s="26">
-        <f>O10*Premissas!$F$71</f>
+        <f>O10*Premissas!$F$71+O11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="P60" s="26">
-        <f>P10*Premissas!$F$71</f>
+        <f>P10*Premissas!$F$71+P11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="Q60" s="26">
-        <f>Q10*Premissas!$F$71</f>
+        <f>Q10*Premissas!$F$71+Q11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="R60" s="26">
-        <f>R10*Premissas!$F$71</f>
+        <f>R10*Premissas!$F$71+R11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="S60" s="26">
-        <f>S10*Premissas!$F$71</f>
+        <f>S10*Premissas!$F$71+S11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="T60" s="26">
-        <f>T10*Premissas!$F$71</f>
+        <f>T10*Premissas!$F$71+T11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="U60" s="26">
-        <f>U10*Premissas!$F$71</f>
+        <f>U10*Premissas!$F$71+U11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="V60" s="26">
-        <f>V10*Premissas!$F$71</f>
+        <f>V10*Premissas!$F$71+V11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="W60" s="26">
-        <f>W10*Premissas!$F$71</f>
+        <f>W10*Premissas!$F$71+W11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="X60" s="26">
-        <f>X10*Premissas!$F$71</f>
+        <f>X10*Premissas!$F$71+X11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="Y60" s="26">
-        <f>Y10*Premissas!$F$71</f>
+        <f>Y10*Premissas!$F$71+Y11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="Z60" s="26">
-        <f>Z10*Premissas!$F$71</f>
+        <f>Z10*Premissas!$F$71+Z11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AA60" s="26">
-        <f>AA10*Premissas!$F$71</f>
+        <f>AA10*Premissas!$F$71+AA11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AB60" s="26">
-        <f>AB10*Premissas!$F$71</f>
+        <f>AB10*Premissas!$F$71+AB11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AC60" s="26">
-        <f>AC10*Premissas!$F$71</f>
+        <f>AC10*Premissas!$F$71+AC11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AD60" s="26">
-        <f>AD10*Premissas!$F$71</f>
+        <f>AD10*Premissas!$F$71+AD11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AE60" s="26">
-        <f>AE10*Premissas!$F$71</f>
+        <f>AE10*Premissas!$F$71+AE11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AF60" s="26">
-        <f>AF10*Premissas!$F$71</f>
+        <f>AF10*Premissas!$F$71+AF11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AG60" s="26">
-        <f>AG10*Premissas!$F$71</f>
+        <f>AG10*Premissas!$F$71+AG11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AH60" s="26">
-        <f>AH10*Premissas!$F$71</f>
+        <f>AH10*Premissas!$F$71+AH11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AI60" s="26">
-        <f>AI10*Premissas!$F$71</f>
+        <f>AI10*Premissas!$F$71+AI11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AJ60" s="26">
-        <f>AJ10*Premissas!$F$71</f>
+        <f>AJ10*Premissas!$F$71+AJ11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AK60" s="26">
-        <f>AK10*Premissas!$F$71</f>
+        <f>AK10*Premissas!$F$71+AK11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AL60" s="26">
-        <f>AL10*Premissas!$F$71</f>
+        <f>AL10*Premissas!$F$71+AL11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AM60" s="26">
-        <f>AM10*Premissas!$F$71</f>
+        <f>AM10*Premissas!$F$71+AM11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AN60" s="26">
-        <f>AN10*Premissas!$F$71</f>
+        <f>AN10*Premissas!$F$71+AN11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AO60" s="26">
-        <f>AO10*Premissas!$F$71</f>
+        <f>AO10*Premissas!$F$71+AO11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AP60" s="26">
-        <f>AP10*Premissas!$F$71</f>
+        <f>AP10*Premissas!$F$71+AP11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AQ60" s="26">
-        <f>AQ10*Premissas!$F$71</f>
+        <f>AQ10*Premissas!$F$71+AQ11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AR60" s="26">
-        <f>AR10*Premissas!$F$71</f>
+        <f>AR10*Premissas!$F$71+AR11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AS60" s="26">
-        <f>AS10*Premissas!$F$71</f>
+        <f>AS10*Premissas!$F$71+AS11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AT60" s="26">
-        <f>AT10*Premissas!$F$71</f>
+        <f>AT10*Premissas!$F$71+AT11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AU60" s="26">
-        <f>AU10*Premissas!$F$71</f>
+        <f>AU10*Premissas!$F$71+AU11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AV60" s="26">
-        <f>AV10*Premissas!$F$71</f>
+        <f>AV10*Premissas!$F$71+AV11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AW60" s="26">
-        <f>AW10*Premissas!$F$71</f>
+        <f>AW10*Premissas!$F$71+AW11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AX60" s="26">
-        <f>AX10*Premissas!$F$71</f>
+        <f>AX10*Premissas!$F$71+AX11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AY60" s="26">
-        <f>AY10*Premissas!$F$71</f>
+        <f>AY10*Premissas!$F$71+AY11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="AZ60" s="26">
-        <f>AZ10*Premissas!$F$71</f>
+        <f>AZ10*Premissas!$F$71+AZ11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BA60" s="26">
-        <f>BA10*Premissas!$F$71</f>
+        <f>BA10*Premissas!$F$71+BA11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BB60" s="26">
-        <f>BB10*Premissas!$F$71</f>
+        <f>BB10*Premissas!$F$71+BB11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BC60" s="26">
-        <f>BC10*Premissas!$F$71</f>
+        <f>BC10*Premissas!$F$71+BC11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BD60" s="26">
-        <f>BD10*Premissas!$F$71</f>
+        <f>BD10*Premissas!$F$71+BD11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BE60" s="26">
-        <f>BE10*Premissas!$F$71</f>
+        <f>BE10*Premissas!$F$71+BE11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BF60" s="26">
-        <f>BF10*Premissas!$F$71</f>
+        <f>BF10*Premissas!$F$71+BF11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BG60" s="26">
-        <f>BG10*Premissas!$F$71</f>
+        <f>BG10*Premissas!$F$71+BG11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BH60" s="26">
-        <f>BH10*Premissas!$F$71</f>
+        <f>BH10*Premissas!$F$71+BH11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BI60" s="26">
-        <f>BI10*Premissas!$F$71</f>
+        <f>BI10*Premissas!$F$71+BI11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BJ60" s="26">
-        <f>BJ10*Premissas!$F$71</f>
+        <f>BJ10*Premissas!$F$71+BJ11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BK60" s="26">
-        <f>BK10*Premissas!$F$71</f>
+        <f>BK10*Premissas!$F$71+BK11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BL60" s="26">
-        <f>BL10*Premissas!$F$71</f>
+        <f>BL10*Premissas!$F$71+BL11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BM60" s="26">
-        <f>BM10*Premissas!$F$71</f>
+        <f>BM10*Premissas!$F$71+BM11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BN60" s="26">
-        <f>BN10*Premissas!$F$71</f>
+        <f>BN10*Premissas!$F$71+BN11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BO60" s="26">
-        <f>BO10*Premissas!$F$71</f>
+        <f>BO10*Premissas!$F$71+BO11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BP60" s="26">
-        <f>BP10*Premissas!$F$71</f>
+        <f>BP10*Premissas!$F$71+BP11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BQ60" s="26">
-        <f>BQ10*Premissas!$F$71</f>
+        <f>BQ10*Premissas!$F$71+BQ11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BR60" s="26">
-        <f>BR10*Premissas!$F$71</f>
+        <f>BR10*Premissas!$F$71+BR11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BS60" s="26">
-        <f>BS10*Premissas!$F$71</f>
+        <f>BS10*Premissas!$F$71+BS11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BT60" s="26">
-        <f>BT10*Premissas!$F$71</f>
+        <f>BT10*Premissas!$F$71+BT11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BU60" s="26">
-        <f>BU10*Premissas!$F$71</f>
+        <f>BU10*Premissas!$F$71+BU11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BV60" s="26">
-        <f>BV10*Premissas!$F$71</f>
+        <f>BV10*Premissas!$F$71+BV11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BW60" s="26">
-        <f>BW10*Premissas!$F$71</f>
+        <f>BW10*Premissas!$F$71+BW11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BX60" s="26">
-        <f>BX10*Premissas!$F$71</f>
+        <f>BX10*Premissas!$F$71+BX11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BY60" s="26">
-        <f>BY10*Premissas!$F$71</f>
+        <f>BY10*Premissas!$F$71+BY11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="BZ60" s="26">
-        <f>BZ10*Premissas!$F$71</f>
+        <f>BZ10*Premissas!$F$71+BZ11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="CA60" s="26">
-        <f>CA10*Premissas!$F$71</f>
+        <f>CA10*Premissas!$F$71+CA11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="CB60" s="26">
-        <f>CB10*Premissas!$F$71</f>
+        <f>CB10*Premissas!$F$71+CB11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="CC60" s="26">
-        <f>CC10*Premissas!$F$71</f>
+        <f>CC10*Premissas!$F$71+CC11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="CD60" s="26">
-        <f>CD10*Premissas!$F$71</f>
+        <f>CD10*Premissas!$F$71+CD11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="CE60" s="26">
-        <f>CE10*Premissas!$F$71</f>
+        <f>CE10*Premissas!$F$71+CE11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="CF60" s="26">
-        <f>CF10*Premissas!$F$71</f>
+        <f>CF10*Premissas!$F$71+CF11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="CG60" s="26">
-        <f>CG10*Premissas!$F$71</f>
+        <f>CG10*Premissas!$F$71+CG11*Premissas!$F$108</f>
         <v/>
       </c>
       <c r="CH60" s="26">
-        <f>CH10*Premissas!$F$71</f>
+        <f>CH10*Premissas!$F$71+CH11*Premissas!$F$108</f>
         <v/>
       </c>
     </row>
@@ -43490,7 +43694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -43590,10 +43794,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -43603,13 +43807,13 @@
         </is>
       </c>
       <c r="B8" s="32" t="n">
-        <v>37190507.8658284</v>
+        <v>44020986.4329842</v>
       </c>
       <c r="C8" s="32" t="n">
-        <v>9634342.415205341</v>
+        <v>14551737.3952747</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>3840284.66676002</v>
+        <v>4842978.20321126</v>
       </c>
     </row>
     <row r="9">
@@ -43619,13 +43823,13 @@
         </is>
       </c>
       <c r="B9" s="34" t="n">
-        <v>0.78363534621863</v>
+        <v>0.754294137062957</v>
       </c>
       <c r="C9" s="34" t="n">
-        <v>0.839478659057499</v>
+        <v>0.8205052934320201</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>0.86690073141928</v>
+        <v>0.857120850717292</v>
       </c>
     </row>
     <row r="10">
@@ -43635,609 +43839,664 @@
         </is>
       </c>
       <c r="B10" s="35" t="n">
-        <v>1.27242857142857</v>
+        <v>1.23280714285714</v>
       </c>
       <c r="C10" s="35" t="n">
-        <v>2.21987878787879</v>
+        <v>2.14617777777778</v>
       </c>
       <c r="D10" s="35" t="n">
-        <v>4.66183333333333</v>
+        <v>4.48399166666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Recuperação do CAC do plano principal (meses)</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>11.2271247333558</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>8.19045538931965</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>5.36269707911766</v>
+          <t>LTV/CAC ponderado pelo mix de novos clientes (mídia paga)</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="n">
+        <v>1.37568118253968</v>
+      </c>
+      <c r="C11" s="35" t="n">
+        <v>2.59122368253968</v>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>6.65219000757576</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mês em que a receita anualizada chega a R$ 50 mi</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>não chega</t>
-        </is>
-      </c>
-      <c r="C12" s="33" t="inlineStr">
-        <is>
-          <t>não chega</t>
-        </is>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>60</v>
+          <t>Recuperação do CAC do plano principal (meses)</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n">
+        <v>12.0608106070809</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>8.78084760546286</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>5.74185756748118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Participação no mercado nesse mês</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="n"/>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n">
-        <v>0.0100310521910908</v>
+          <t>Mês em que a receita anualizada chega a R$ 50 mi</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>não chega</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>não chega</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Receita por pessoa no ano 5</t>
-        </is>
-      </c>
-      <c r="B14" s="32" t="n">
-        <v>167417.658371133</v>
-      </c>
-      <c r="C14" s="32" t="n">
-        <v>334474.961211361</v>
-      </c>
-      <c r="D14" s="32" t="n">
-        <v>618215.343992554</v>
+          <t>Participação no mercado nesse mês</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n">
+        <v>0.0100310521910908</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Receita por pessoa no ano 5</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="n">
+        <v>167417.658371134</v>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>334474.961211361</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>618215.343992554</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Clientes ativos no ano 5</t>
         </is>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B16" s="37" t="n">
         <v>948.553580176207</v>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C16" s="37" t="n">
         <v>2126.49894963504</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D16" s="37" t="n">
         <v>4564.12874694633</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Modelo B: agência operada por agentes</t>
-        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Indicador</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Otimista</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Modelo B: agência operada por agentes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Receita recorrente anualizada no ano 5</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="n">
-        <v>22289517.3070338</v>
-      </c>
-      <c r="C19" s="32" t="n">
-        <v>52944478.3690642</v>
-      </c>
-      <c r="D19" s="32" t="n">
-        <v>120301477.71446</v>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Otimista</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Receita recorrente anualizada no ano 7</t>
+          <t>Receita recorrente anualizada no ano 5</t>
         </is>
       </c>
       <c r="B20" s="32" t="n">
-        <v>40308823.7075543</v>
+        <v>14804180.7184473</v>
       </c>
       <c r="C20" s="32" t="n">
-        <v>99378476.6764778</v>
+        <v>34605228.5960912</v>
       </c>
       <c r="D20" s="32" t="n">
-        <v>248847772.010338</v>
+        <v>77481259.6928158</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mês de equilíbrio (EBITDA positivo daí em diante)</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="n">
-        <v>80</v>
-      </c>
-      <c r="C21" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="D21" s="33" t="n">
-        <v>26</v>
+          <t>Receita recorrente anualizada no ano 7</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="n">
+        <v>25174222.3467315</v>
+      </c>
+      <c r="C21" s="32" t="n">
+        <v>60631762.6956647</v>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>150224284.237322</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Capital necessário (pior caixa acumulado)</t>
-        </is>
-      </c>
-      <c r="B22" s="32" t="n">
-        <v>22213111.8388837</v>
-      </c>
-      <c r="C22" s="32" t="n">
-        <v>4893226.25639397</v>
-      </c>
-      <c r="D22" s="32" t="n">
-        <v>1956033.46953018</v>
+          <t>Mês de equilíbrio (EBITDA positivo daí em diante)</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>não chega</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="n">
+        <v>56</v>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Margem bruta no ano 5</t>
-        </is>
-      </c>
-      <c r="B23" s="34" t="n">
-        <v>0.608900373225557</v>
-      </c>
-      <c r="C23" s="34" t="n">
-        <v>0.7236789117304</v>
-      </c>
-      <c r="D23" s="34" t="n">
-        <v>0.806277484609826</v>
+          <t>Capital necessário (pior caixa acumulado)</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="n">
+        <v>55143316.0510048</v>
+      </c>
+      <c r="C23" s="32" t="n">
+        <v>12489561.4335821</v>
+      </c>
+      <c r="D23" s="32" t="n">
+        <v>4327759.42482551</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LTV/CAC do plano principal (Consultório / Agenda Cheia), mídia paga</t>
-        </is>
-      </c>
-      <c r="B24" s="35" t="n">
-        <v>3.47511111111111</v>
-      </c>
-      <c r="C24" s="35" t="n">
-        <v>8.04484848484849</v>
-      </c>
-      <c r="D24" s="35" t="n">
-        <v>19.6425</v>
+          <t>Margem bruta no ano 5</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="n">
+        <v>0.402979636158557</v>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>0.602800849409423</v>
+      </c>
+      <c r="D24" s="34" t="n">
+        <v>0.718748570922122</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Recuperação do CAC do plano principal (meses)</t>
-        </is>
-      </c>
-      <c r="B25" s="36" t="n">
-        <v>7.19401457986955</v>
-      </c>
-      <c r="C25" s="36" t="n">
-        <v>4.14343830043694</v>
-      </c>
-      <c r="D25" s="36" t="n">
-        <v>2.54550082728777</v>
+          <t>LTV/CAC do plano principal (Consultório / Agenda Cheia), mídia paga</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="n">
+        <v>1.10748717948718</v>
+      </c>
+      <c r="C25" s="35" t="n">
+        <v>2.87906666666667</v>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>7.18153333333333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mês em que a receita anualizada chega a R$ 50 mi</t>
-        </is>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>não chega</t>
-        </is>
-      </c>
-      <c r="C26" s="33" t="n">
-        <v>58</v>
-      </c>
-      <c r="D26" s="33" t="n">
-        <v>42</v>
+          <t>LTV/CAC ponderado pelo mix de novos clientes (mídia paga)</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="n">
+        <v>1.00794623233909</v>
+      </c>
+      <c r="C26" s="35" t="n">
+        <v>2.65395487179487</v>
+      </c>
+      <c r="D26" s="35" t="n">
+        <v>6.68894381447124</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Participação no mercado nesse mês</t>
-        </is>
-      </c>
-      <c r="B27" s="34" t="n"/>
-      <c r="C27" s="34" t="n">
-        <v>0.00742498264357183</v>
-      </c>
-      <c r="D27" s="34" t="n">
-        <v>0.00499407117545784</v>
+          <t>Recuperação do CAC do plano principal (meses)</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="n">
+        <v>14.7654750381441</v>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>7.29356408424628</v>
+      </c>
+      <c r="D27" s="36" t="n">
+        <v>4.78684192890582</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Receita por pessoa no ano 5</t>
-        </is>
-      </c>
-      <c r="B28" s="32" t="n">
-        <v>243010.074370012</v>
-      </c>
-      <c r="C28" s="32" t="n">
-        <v>439865.521496465</v>
-      </c>
-      <c r="D28" s="32" t="n">
-        <v>715302.316447779</v>
+          <t>Mês em que a receita anualizada chega a R$ 50 mi</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>não chega</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="D28" s="33" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Clientes ativos no ano 5</t>
-        </is>
-      </c>
-      <c r="B29" s="37" t="n">
-        <v>1140.52640543871</v>
-      </c>
-      <c r="C29" s="37" t="n">
-        <v>2591.44154405227</v>
-      </c>
-      <c r="D29" s="37" t="n">
-        <v>5094.24060108116</v>
+          <t>Participação no mercado nesse mês</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="34" t="n">
+        <v>0.008253008431881681</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <v>0.00562895939230752</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Receita por pessoa no ano 5</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="n">
+        <v>162593.255397265</v>
+      </c>
+      <c r="C30" s="32" t="n">
+        <v>301399.11371929</v>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>478291.894915521</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Testes de estresse do Modelo B (cenário base, uma aposta por vez)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Receita recorrente anualizada no ano 5</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Receita recorrente anualizada no ano 7</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Mês de equilíbrio (EBITDA positivo daí em diante)</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Capital necessário (pior caixa acumulado)</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Margem bruta no ano 5</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>LTV/CAC do plano principal (Consultório / Agenda Cheia), mídia paga</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Recuperação do CAC do plano principal (meses)</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Mês em que a receita anualizada chega a R$ 50 mi</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>Participação no mercado nesse mês</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>Receita por pessoa no ano 5</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Clientes ativos no ano 5</t>
         </is>
+      </c>
+      <c r="B31" s="37" t="n">
+        <v>792.8287312231849</v>
+      </c>
+      <c r="C31" s="37" t="n">
+        <v>1855.9641785283</v>
+      </c>
+      <c r="D31" s="37" t="n">
+        <v>3914.07897082428</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>B com churn igual ao do Modelo A</t>
-        </is>
-      </c>
-      <c r="B33" s="32" t="n">
-        <v>40059184.7586515</v>
-      </c>
-      <c r="C33" s="32" t="n">
-        <v>69243590.22671761</v>
-      </c>
-      <c r="D33" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="E33" s="32" t="n">
-        <v>5458402.99335927</v>
-      </c>
-      <c r="F33" s="34" t="n">
-        <v>0.727079456253982</v>
-      </c>
-      <c r="G33" s="35" t="n">
-        <v>4.38809917355372</v>
-      </c>
-      <c r="H33" s="36" t="n">
-        <v>4.14343830043694</v>
-      </c>
-      <c r="I33" s="33" t="n">
-        <v>68</v>
-      </c>
-      <c r="J33" s="34" t="n">
-        <v>0.00743380595370213</v>
-      </c>
-      <c r="K33" s="32" t="n">
-        <v>396442.657066252</v>
-      </c>
-      <c r="L33" s="37" t="n">
-        <v>1955.29160734211</v>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Testes de estresse do Modelo B (cenário base, uma aposta por vez)</t>
+        </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>B com metade das contas por especialista</t>
-        </is>
-      </c>
-      <c r="B34" s="32" t="n">
-        <v>52944478.3690642</v>
-      </c>
-      <c r="C34" s="32" t="n">
-        <v>99378476.6764778</v>
-      </c>
-      <c r="D34" s="33" t="n">
-        <v>39</v>
-      </c>
-      <c r="E34" s="32" t="n">
-        <v>6116493.76611212</v>
-      </c>
-      <c r="F34" s="34" t="n">
-        <v>0.577023205026721</v>
-      </c>
-      <c r="G34" s="35" t="n">
-        <v>6.52969696969697</v>
-      </c>
-      <c r="H34" s="36" t="n">
-        <v>5.10488212363096</v>
-      </c>
-      <c r="I34" s="33" t="n">
-        <v>58</v>
-      </c>
-      <c r="J34" s="34" t="n">
-        <v>0.00742498264357183</v>
-      </c>
-      <c r="K34" s="32" t="n">
-        <v>289855.365747823</v>
-      </c>
-      <c r="L34" s="37" t="n">
-        <v>2591.44154405227</v>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Receita recorrente anualizada no ano 5</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Receita recorrente anualizada no ano 7</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Mês de equilíbrio (EBITDA positivo daí em diante)</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Capital necessário (pior caixa acumulado)</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Margem bruta no ano 5</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>LTV/CAC do plano principal (Consultório / Agenda Cheia), mídia paga</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>LTV/CAC ponderado pelo mix de novos clientes (mídia paga)</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Recuperação do CAC do plano principal (meses)</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>Mês em que a receita anualizada chega a R$ 50 mi</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>Participação no mercado nesse mês</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Receita por pessoa no ano 5</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>Clientes ativos no ano 5</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B sem receita por consulta</t>
+          <t>B se as apostas se confirmarem (churn de agência, 40 a 70 contas por especialista, CAC R$ 5.500)</t>
         </is>
       </c>
       <c r="B35" s="32" t="n">
-        <v>47243823.7236057</v>
+        <v>47196517.3421754</v>
       </c>
       <c r="C35" s="32" t="n">
-        <v>88558332.3246356</v>
+        <v>88530926.7016255</v>
       </c>
       <c r="D35" s="33" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E35" s="32" t="n">
-        <v>5604635.46859475</v>
+        <v>7937541.84431522</v>
       </c>
       <c r="F35" s="34" t="n">
-        <v>0.692327136776724</v>
+        <v>0.661087536710487</v>
       </c>
       <c r="G35" s="35" t="n">
-        <v>6.48121212121212</v>
-      </c>
-      <c r="H35" s="36" t="n">
-        <v>5.14307088086778</v>
-      </c>
-      <c r="I35" s="33" t="n">
+        <v>6.06806060606061</v>
+      </c>
+      <c r="H35" s="35" t="n">
+        <v>5.04638714791702</v>
+      </c>
+      <c r="I35" s="36" t="n">
+        <v>5.6437462161247</v>
+      </c>
+      <c r="J35" s="33" t="n">
         <v>62</v>
       </c>
-      <c r="J35" s="34" t="n">
-        <v>0.008454677613327201</v>
-      </c>
-      <c r="K35" s="32" t="n">
-        <v>395043.353251387</v>
-      </c>
-      <c r="L35" s="37" t="n">
-        <v>2591.44154405227</v>
+      <c r="K35" s="34" t="n">
+        <v>0.0084514150221945</v>
+      </c>
+      <c r="L35" s="32" t="n">
+        <v>394735.126807427</v>
+      </c>
+      <c r="M35" s="37" t="n">
+        <v>2590.34523754594</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B com preço 30% menor (R$ 690 / R$ 1.250)</t>
+          <t>B com cobrança de R$ 30 por consulta (só com parecer jurídico favorável)</t>
         </is>
       </c>
       <c r="B36" s="32" t="n">
-        <v>38683345.3527024</v>
+        <v>38907850.2102973</v>
       </c>
       <c r="C36" s="32" t="n">
-        <v>72647819.23983251</v>
+        <v>68322313.917432</v>
       </c>
       <c r="D36" s="33" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E36" s="32" t="n">
-        <v>7921857.08558312</v>
+        <v>9358328.542410141</v>
       </c>
       <c r="F36" s="34" t="n">
-        <v>0.628648219128262</v>
+        <v>0.643871915719431</v>
       </c>
       <c r="G36" s="35" t="n">
-        <v>5.23030303030303</v>
-      </c>
-      <c r="H36" s="36" t="n">
-        <v>6.37311703360371</v>
-      </c>
-      <c r="I36" s="33" t="n">
+        <v>3.62398974358974</v>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>3.21264717948718</v>
+      </c>
+      <c r="I36" s="36" t="n">
+        <v>5.73547967728368</v>
+      </c>
+      <c r="J36" s="33" t="n">
         <v>69</v>
       </c>
-      <c r="J36" s="34" t="n">
-        <v>0.0103610222005855</v>
-      </c>
-      <c r="K36" s="32" t="n">
-        <v>327301.835760305</v>
-      </c>
-      <c r="L36" s="37" t="n">
-        <v>2591.44154405227</v>
+      <c r="K36" s="34" t="n">
+        <v>0.00721958567159208</v>
+      </c>
+      <c r="L36" s="32" t="n">
+        <v>336158.470062527</v>
+      </c>
+      <c r="M36" s="37" t="n">
+        <v>1855.9641785283</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B com tudo isso junto</t>
+          <t>B com as apostas confirmadas e cobrança por consulta (o base da v2)</t>
         </is>
       </c>
       <c r="B37" s="32" t="n">
-        <v>24959583.4209446</v>
+        <v>52884367.7267087</v>
       </c>
       <c r="C37" s="32" t="n">
-        <v>43096568.7076997</v>
-      </c>
-      <c r="D37" s="33" t="inlineStr">
-        <is>
-          <t>não chega</t>
-        </is>
+        <v>99344534.35000069</v>
+      </c>
+      <c r="D37" s="33" t="n">
+        <v>39</v>
       </c>
       <c r="E37" s="32" t="n">
-        <v>36098232.5646127</v>
+        <v>6532844.09032664</v>
       </c>
       <c r="F37" s="34" t="n">
-        <v>0.354128296514166</v>
+        <v>0.695564310040968</v>
       </c>
       <c r="G37" s="35" t="n">
-        <v>1.17355371900826</v>
-      </c>
-      <c r="H37" s="36" t="n">
-        <v>15.4929577464789</v>
-      </c>
-      <c r="I37" s="33" t="inlineStr">
-        <is>
-          <t>não chega</t>
-        </is>
-      </c>
-      <c r="J37" s="34" t="n"/>
-      <c r="K37" s="32" t="n">
-        <v>176944.185896645</v>
-      </c>
-      <c r="L37" s="37" t="n">
-        <v>1955.29160734211</v>
+        <v>7.53533333333333</v>
+      </c>
+      <c r="H37" s="35" t="n">
+        <v>5.98344086692528</v>
+      </c>
+      <c r="I37" s="36" t="n">
+        <v>4.52068418500284</v>
+      </c>
+      <c r="J37" s="33" t="n">
+        <v>59</v>
+      </c>
+      <c r="K37" s="34" t="n">
+        <v>0.00763795704121761</v>
+      </c>
+      <c r="L37" s="32" t="n">
+        <v>439438.142719752</v>
+      </c>
+      <c r="M37" s="37" t="n">
+        <v>2590.34523754594</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>B com o dobro de contas por especialista, sem mudar o resto</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="n">
+        <v>34605228.5960912</v>
+      </c>
+      <c r="C38" s="32" t="n">
+        <v>60631762.6956647</v>
+      </c>
+      <c r="D38" s="33" t="n">
+        <v>51</v>
+      </c>
+      <c r="E38" s="32" t="n">
+        <v>9248513.847218631</v>
+      </c>
+      <c r="F38" s="34" t="n">
+        <v>0.713534438129155</v>
+      </c>
+      <c r="G38" s="35" t="n">
+        <v>3.39188717948718</v>
+      </c>
+      <c r="H38" s="35" t="n">
+        <v>3.14113435897436</v>
+      </c>
+      <c r="I38" s="36" t="n">
+        <v>6.14446100472966</v>
+      </c>
+      <c r="J38" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="K38" s="34" t="n">
+        <v>0.008253008431881681</v>
+      </c>
+      <c r="L38" s="32" t="n">
+        <v>408563.863203761</v>
+      </c>
+      <c r="M38" s="37" t="n">
+        <v>1855.9641785283</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B com churn de agência com contrato, sem mudar o resto</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="n">
+        <v>43360492.6695094</v>
+      </c>
+      <c r="C39" s="32" t="n">
+        <v>81127015.60933989</v>
+      </c>
+      <c r="D39" s="33" t="n">
+        <v>51</v>
+      </c>
+      <c r="E39" s="32" t="n">
+        <v>9925656.44506189</v>
+      </c>
+      <c r="F39" s="34" t="n">
+        <v>0.603950941229627</v>
+      </c>
+      <c r="G39" s="35" t="n">
+        <v>4.70716239316239</v>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>3.9026570984571</v>
+      </c>
+      <c r="I39" s="36" t="n">
+        <v>7.29356408424628</v>
+      </c>
+      <c r="J39" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="K39" s="34" t="n">
+        <v>0.00854173631539736</v>
+      </c>
+      <c r="L39" s="32" t="n">
+        <v>323042.425710392</v>
+      </c>
+      <c r="M39" s="37" t="n">
+        <v>2379.72299699474</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Sem expansão para dentistas</t>
         </is>
       </c>
-      <c r="B38" s="32" t="n">
-        <v>32115848.5914442</v>
-      </c>
-      <c r="C38" s="32" t="n">
-        <v>59050763.8189698</v>
-      </c>
-      <c r="D38" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="E38" s="32" t="n">
-        <v>5834410.3242267</v>
-      </c>
-      <c r="F38" s="34" t="n">
-        <v>0.723253542853639</v>
-      </c>
-      <c r="G38" s="35" t="n">
-        <v>8.04484848484849</v>
-      </c>
-      <c r="H38" s="36" t="n">
-        <v>4.14343830043694</v>
-      </c>
-      <c r="I38" s="33" t="n">
-        <v>76</v>
-      </c>
-      <c r="J38" s="34" t="n">
-        <v>0.0162213909110967</v>
-      </c>
-      <c r="K38" s="32" t="n">
-        <v>339865.888752581</v>
-      </c>
-      <c r="L38" s="37" t="n">
-        <v>1570.42797887879</v>
+      <c r="B40" s="32" t="n">
+        <v>20736220.1457016</v>
+      </c>
+      <c r="C40" s="32" t="n">
+        <v>35830707.4494798</v>
+      </c>
+      <c r="D40" s="33" t="n">
+        <v>81</v>
+      </c>
+      <c r="E40" s="32" t="n">
+        <v>19276294.9469606</v>
+      </c>
+      <c r="F40" s="34" t="n">
+        <v>0.603092179131503</v>
+      </c>
+      <c r="G40" s="35" t="n">
+        <v>2.87906666666667</v>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>2.65395487179487</v>
+      </c>
+      <c r="I40" s="36" t="n">
+        <v>7.29356408424628</v>
+      </c>
+      <c r="J40" s="33" t="inlineStr">
+        <is>
+          <t>não chega</t>
+        </is>
+      </c>
+      <c r="K40" s="34" t="n"/>
+      <c r="L40" s="32" t="n">
+        <v>230177.777294263</v>
+      </c>
+      <c r="M40" s="37" t="n">
+        <v>1110.32025466001</v>
       </c>
     </row>
   </sheetData>
@@ -44251,7 +44510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -44348,14 +44607,14 @@
         <v>16530032.9455546</v>
       </c>
       <c r="G5" s="32" t="n">
-        <v>12209729.4502695</v>
+        <v>19630809.6348875</v>
       </c>
       <c r="H5" s="32" t="n">
-        <v>6949653.81217204</v>
+        <v>9444707.377303859</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.7x / 3.3x</t>
+          <t>1.6x / 3.2x</t>
         </is>
       </c>
     </row>
@@ -44381,14 +44640,14 @@
         <v>7957489.321805097</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>12005449.4219147</v>
+        <v>19124212.1699428</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>8057001.77256252</v>
+        <v>11626534.8279476</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.5x / 2.9x</t>
+          <t>1.5x / 2.8x</t>
         </is>
       </c>
     </row>
@@ -44414,14 +44673,14 @@
         <v>10490446.3986437</v>
       </c>
       <c r="G7" s="32" t="n">
-        <v>11981980.4281638</v>
+        <v>19021796.9306925</v>
       </c>
       <c r="H7" s="32" t="n">
-        <v>8400665.733010869</v>
+        <v>12358773.8997766</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.2x / 2.2x</t>
+          <t>2.1x / 2.1x</t>
         </is>
       </c>
     </row>
@@ -44447,14 +44706,14 @@
         <v>6378013.478004105</v>
       </c>
       <c r="G8" s="32" t="n">
-        <v>10440825.4148472</v>
+        <v>16213738.7172976</v>
       </c>
       <c r="H8" s="32" t="n">
-        <v>8802366.97548539</v>
+        <v>12967525.0303691</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.7x / 3.1x</t>
+          <t>1.7x / 2.9x</t>
         </is>
       </c>
     </row>
@@ -44480,14 +44739,14 @@
         <v>5261864.050279297</v>
       </c>
       <c r="G9" s="32" t="n">
-        <v>10308592.3411012</v>
+        <v>15737539.573298</v>
       </c>
       <c r="H9" s="32" t="n">
-        <v>8982593.55598993</v>
+        <v>13450833.3068843</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.2x / 2.2x</t>
+          <t>2.1x / 2.1x</t>
         </is>
       </c>
     </row>
@@ -44513,14 +44772,14 @@
         <v>2287342.076159701</v>
       </c>
       <c r="G10" s="32" t="n">
-        <v>9975642.8843085</v>
+        <v>15226252.7692951</v>
       </c>
       <c r="H10" s="32" t="n">
-        <v>9327944.68330444</v>
+        <v>13933187.8205369</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.2x / 2.2x</t>
+          <t>2.1x / 2.1x</t>
         </is>
       </c>
     </row>
@@ -44546,21 +44805,21 @@
         <v>0</v>
       </c>
       <c r="G11" s="32" t="n">
-        <v>10046720.0833298</v>
+        <v>15303495.8971482</v>
       </c>
       <c r="H11" s="32" t="n">
-        <v>9368794.375936471</v>
+        <v>14066164.3139725</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.1x / 2.3x</t>
+          <t>2.0x / 2.2x</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Base: ARR ano 7 = R$ 37.026.396; capital necessário = R$ 9.634.342</t>
+          <t>Base: ARR ano 7 = R$ 37.026.396; capital necessário = R$ 14.551.737</t>
         </is>
       </c>
     </row>
@@ -44621,66 +44880,66 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CAC na mídia paga</t>
+          <t>Preço da Agenda Cheia</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7500</v>
+        <v>1290</v>
       </c>
       <c r="C16" t="n">
-        <v>4000</v>
+        <v>2290</v>
       </c>
       <c r="D16" s="32" t="n">
-        <v>84974461.274629</v>
+        <v>52851814.9301591</v>
       </c>
       <c r="E16" s="32" t="n">
-        <v>119634123.335328</v>
+        <v>68411710.4611703</v>
       </c>
       <c r="F16" s="32" t="n">
-        <v>34659662.060699</v>
+        <v>15559895.5310112</v>
       </c>
       <c r="G16" s="32" t="n">
-        <v>5628781.31820959</v>
+        <v>19693977.4596017</v>
       </c>
       <c r="H16" s="32" t="n">
-        <v>4076732.66205948</v>
+        <v>9143550.135030201</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.9x / 11.1x</t>
+          <t>1.6x / 4.1x</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Preço da Agenda Cheia</t>
+          <t>CAC na mídia paga</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1290</v>
+        <v>9000</v>
       </c>
       <c r="C17" t="n">
-        <v>2290</v>
+        <v>5000</v>
       </c>
       <c r="D17" s="32" t="n">
-        <v>87379891.0939697</v>
+        <v>52131039.1288989</v>
       </c>
       <c r="E17" s="32" t="n">
-        <v>111377062.258986</v>
+        <v>69812544.14777181</v>
       </c>
       <c r="F17" s="32" t="n">
-        <v>23997171.16501629</v>
+        <v>17681505.01887291</v>
       </c>
       <c r="G17" s="32" t="n">
-        <v>5802781.5044529</v>
+        <v>16346275.2079351</v>
       </c>
       <c r="H17" s="32" t="n">
-        <v>4183551.11224206</v>
+        <v>9864382.972524291</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.4x / 10.7x</t>
+          <t>2.1x / 3.7x</t>
         </is>
       </c>
     </row>
@@ -44691,95 +44950,95 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.05</v>
+        <v>0.065</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D18" s="32" t="n">
-        <v>84732614.99028949</v>
+        <v>55298075.5105228</v>
       </c>
       <c r="E18" s="32" t="n">
-        <v>110590719.077347</v>
+        <v>71845203.64442579</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>25858104.0870575</v>
+        <v>16547128.133903</v>
       </c>
       <c r="G18" s="32" t="n">
-        <v>5186799.21307364</v>
+        <v>13765012.5621523</v>
       </c>
       <c r="H18" s="32" t="n">
-        <v>4730550.86815986</v>
+        <v>10810516.3357528</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.8x / 12.1x</t>
+          <t>2.2x / 4.7x</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Consultas atribuídas por cliente</t>
+          <t>Preço por consulta atribuída</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D19" s="32" t="n">
-        <v>92179325.32697301</v>
+        <v>60631762.6956647</v>
       </c>
       <c r="E19" s="32" t="n">
-        <v>106577628.025983</v>
+        <v>68322313.917432</v>
       </c>
       <c r="F19" s="32" t="n">
-        <v>14398302.69901</v>
+        <v>7690551.221767299</v>
       </c>
       <c r="G19" s="32" t="n">
-        <v>5389528.7514859</v>
+        <v>12489561.4335821</v>
       </c>
       <c r="H19" s="32" t="n">
-        <v>4465646.56860585</v>
+        <v>9358328.542410141</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6.5x / 9.6x</t>
+          <t>2.9x / 3.6x</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Indicação (% da base por mês)</t>
+          <t>Contas por especialista (Agenda Cheia)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.005</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>0.015</v>
+        <v>50</v>
       </c>
       <c r="D20" s="32" t="n">
-        <v>90629414.0603729</v>
+        <v>60631762.6956647</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>109600007.949421</v>
+        <v>60631762.6956647</v>
       </c>
       <c r="F20" s="32" t="n">
-        <v>18970593.8890481</v>
+        <v>0</v>
       </c>
       <c r="G20" s="32" t="n">
-        <v>5055179.19736323</v>
+        <v>14820730.8900366</v>
       </c>
       <c r="H20" s="32" t="n">
-        <v>4726052.58713563</v>
+        <v>11044277.0280397</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.0x / 8.0x</t>
+          <t>2.4x / 3.3x</t>
         </is>
       </c>
     </row>
@@ -44790,102 +45049,135 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.055</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="D21" s="32" t="n">
-        <v>89902730.45910449</v>
+        <v>56686721.8142317</v>
       </c>
       <c r="E21" s="32" t="n">
-        <v>106507239.838706</v>
+        <v>68817424.5369004</v>
       </c>
       <c r="F21" s="32" t="n">
-        <v>16604509.37960151</v>
+        <v>12130702.7226687</v>
       </c>
       <c r="G21" s="32" t="n">
-        <v>5058722.99469001</v>
+        <v>13400853.6297017</v>
       </c>
       <c r="H21" s="32" t="n">
-        <v>4797577.36857815</v>
+        <v>11131735.8806012</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8.0x / 8.0x</t>
+          <t>2.9x / 2.9x</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Contas por especialista (Agenda Cheia)</t>
+          <t>Custo dos agentes por conta (Agenda Cheia)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="C22" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>99378476.6764778</v>
+        <v>60631762.6956647</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>99378476.6764778</v>
+        <v>60631762.6956647</v>
       </c>
       <c r="F22" s="32" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>5448722.00914539</v>
+        <v>15069944.9978893</v>
       </c>
       <c r="H22" s="32" t="n">
-        <v>4721748.4725522</v>
+        <v>11708226.9358687</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.5x / 8.5x</t>
+          <t>2.3x / 3.1x</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Custo dos agentes por conta (Agenda Cheia)</t>
+          <t>Contas por especialista (Presença)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>400</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="D23" s="32" t="n">
-        <v>99378476.6764778</v>
+        <v>60631762.6956647</v>
       </c>
       <c r="E23" s="32" t="n">
-        <v>99378476.6764778</v>
+        <v>60631762.6956647</v>
       </c>
       <c r="F23" s="32" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="32" t="n">
-        <v>5285353.61806312</v>
+        <v>13935982.9299362</v>
       </c>
       <c r="H23" s="32" t="n">
-        <v>4747526.72409533</v>
+        <v>11155128.5101524</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7.0x / 8.5x</t>
+          <t>2.9x / 2.9x</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Base: ARR ano 7 = R$ 99.378.477; capital necessário = R$ 4.893.226</t>
+          <t>Indicação (% da base por mês)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D24" s="32" t="n">
+        <v>56314643.0824065</v>
+      </c>
+      <c r="E24" s="32" t="n">
+        <v>65561170.5373595</v>
+      </c>
+      <c r="F24" s="32" t="n">
+        <v>9246527.454953</v>
+      </c>
+      <c r="G24" s="32" t="n">
+        <v>13286448.3101787</v>
+      </c>
+      <c r="H24" s="32" t="n">
+        <v>11731195.0057815</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2.9x / 2.9x</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Base: ARR ano 7 = R$ 60.631.763; capital necessário = R$ 12.489.561</t>
         </is>
       </c>
     </row>
